--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>2026-10-01T02:25:09.097838Z</t>
+  </si>
+  <si>
+    <t>2026-10-01T09:26:20.107793Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1000,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1078,8 +1081,31 @@
         <v>534.89</v>
       </c>
     </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5">
+        <v>339.3909301757812</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.5627515316009521</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="H4" s="5">
+        <v>-9.5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>534.89</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I3"/>
+  <autoFilter ref="A2:I4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1101,7 +1127,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1116,39 +1142,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1174,17 +1200,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1192,202 +1218,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>2026-10-01T09:26:20.107793Z</t>
+  </si>
+  <si>
+    <t>2026-10-01T16:42:42.229070Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1003,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1104,8 +1107,31 @@
         <v>534.89</v>
       </c>
     </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5">
+        <v>2060.4169921875</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6.204731941223145</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="H5" s="5">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="I5" s="5">
+        <v>531.38</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I4"/>
+  <autoFilter ref="A2:I5"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1127,7 +1153,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1142,39 +1168,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1200,17 +1226,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1218,202 +1244,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>2026-10-01T16:42:42.229070Z</t>
+  </si>
+  <si>
+    <t>2026-10-01T21:23:16.688131Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1006,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1130,8 +1133,31 @@
         <v>531.38</v>
       </c>
     </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5">
+        <v>628.7714233398438</v>
+      </c>
+      <c r="F6" s="5">
+        <v>21.36655426025391</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H6" s="5">
+        <v>-11.68</v>
+      </c>
+      <c r="I6" s="5">
+        <v>535.8200000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I5"/>
+  <autoFilter ref="A2:I6"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1153,7 +1179,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1168,39 +1194,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1226,17 +1252,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1244,202 +1270,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>2026-10-01T21:23:16.688131Z</t>
+  </si>
+  <si>
+    <t>2026-10-02T01:13:46.292641Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1009,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1156,8 +1159,31 @@
         <v>535.8200000000001</v>
       </c>
     </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5">
+        <v>156.4220275878906</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3.230470180511475</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H7" s="5">
+        <v>-11.68</v>
+      </c>
+      <c r="I7" s="5">
+        <v>535.8200000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I6"/>
+  <autoFilter ref="A2:I7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1179,7 +1205,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1194,39 +1220,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1252,17 +1278,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1270,202 +1296,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>2026-10-02T01:13:46.292641Z</t>
+  </si>
+  <si>
+    <t>2026-10-02T07:31:44.881369Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1012,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1182,8 +1185,31 @@
         <v>535.8200000000001</v>
       </c>
     </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5">
+        <v>173.2319641113281</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.7507917284965515</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H8" s="5">
+        <v>-11.1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>555.33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I7"/>
+  <autoFilter ref="A2:I8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1205,7 +1231,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1220,39 +1246,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1278,17 +1304,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1296,202 +1322,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="109">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -147,6 +147,9 @@
   </si>
   <si>
     <t>2026-10-02T07:31:44.881369Z</t>
+  </si>
+  <si>
+    <t>2026-10-02T14:09:46.276776Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1015,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1208,8 +1211,31 @@
         <v>555.33</v>
       </c>
     </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5">
+        <v>651.74267578125</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1.206049799919128</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="H9" s="5">
+        <v>-3.23</v>
+      </c>
+      <c r="I9" s="5">
+        <v>528.34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I8"/>
+  <autoFilter ref="A2:I9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1231,7 +1257,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1246,39 +1272,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1304,17 +1330,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1322,202 +1348,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>2026-10-02T14:09:46.276776Z</t>
+  </si>
+  <si>
+    <t>2026-10-02T23:15:39.765184Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1018,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1234,8 +1237,37 @@
         <v>528.34</v>
       </c>
     </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-0.41</v>
+      </c>
+      <c r="D10" s="5">
+        <v>283.88</v>
+      </c>
+      <c r="E10" s="5">
+        <v>342.2538452148438</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7.730380535125732</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="H10" s="5">
+        <v>-3.31</v>
+      </c>
+      <c r="I10" s="5">
+        <v>386.9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I9"/>
+  <autoFilter ref="A2:I10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1257,7 +1289,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1272,39 +1304,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1330,17 +1362,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1348,202 +1380,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>2026-10-02T23:15:39.765184Z</t>
+  </si>
+  <si>
+    <t>2026-10-03T02:19:56.238503Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1021,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1266,8 +1269,31 @@
         <v>386.9</v>
       </c>
     </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5">
+        <v>303.5421447753906</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2.036928415298462</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="H11" s="5">
+        <v>-2.66</v>
+      </c>
+      <c r="I11" s="5">
+        <v>374.03</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I10"/>
+  <autoFilter ref="A2:I11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1289,7 +1315,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1304,39 +1330,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1362,17 +1388,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1380,202 +1406,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>2026-10-03T02:19:56.238503Z</t>
+  </si>
+  <si>
+    <t>2026-10-03T08:34:28.334981Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1024,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1292,8 +1295,31 @@
         <v>374.03</v>
       </c>
     </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5">
+        <v>118.4067153930664</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.7667706608772278</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H12" s="5">
+        <v>-4.19</v>
+      </c>
+      <c r="I12" s="5">
+        <v>375.81</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I11"/>
+  <autoFilter ref="A2:I12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1315,7 +1341,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1330,39 +1356,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1388,17 +1414,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1406,202 +1432,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>2026-10-03T08:34:28.334981Z</t>
+  </si>
+  <si>
+    <t>2026-10-03T13:57:29.010670Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1027,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1318,8 +1321,31 @@
         <v>375.81</v>
       </c>
     </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5">
+        <v>472.7425231933594</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.6435344219207764</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="H13" s="5">
+        <v>-5.87</v>
+      </c>
+      <c r="I13" s="5">
+        <v>365.84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I12"/>
+  <autoFilter ref="A2:I13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1341,7 +1367,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1356,39 +1382,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1414,17 +1440,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1432,202 +1458,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>2026-10-03T13:57:29.010670Z</t>
+  </si>
+  <si>
+    <t>2026-10-03T18:17:16.226552Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1030,7 +1033,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1344,8 +1347,35 @@
         <v>365.84</v>
       </c>
     </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5">
+        <v>2.28</v>
+      </c>
+      <c r="D14" s="5">
+        <v>284.71</v>
+      </c>
+      <c r="E14" s="5">
+        <v>141.0826568603516</v>
+      </c>
+      <c r="F14" s="5">
+        <v>5.628716945648193</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H14" s="5">
+        <v>-2.48</v>
+      </c>
+      <c r="I14" s="5">
+        <v>355.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I13"/>
+  <autoFilter ref="A2:I14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1367,7 +1397,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1382,39 +1412,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1440,17 +1470,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1458,202 +1488,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>2026-10-03T18:17:16.226552Z</t>
+  </si>
+  <si>
+    <t>2026-10-03T21:50:24.795096Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1033,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1374,8 +1377,31 @@
         <v>355.83</v>
       </c>
     </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5">
+        <v>228.9217071533203</v>
+      </c>
+      <c r="F15" s="5">
+        <v>8.886663436889648</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="H15" s="5">
+        <v>-2.34</v>
+      </c>
+      <c r="I15" s="5">
+        <v>355.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I14"/>
+  <autoFilter ref="A2:I15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1397,7 +1423,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1412,39 +1438,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1470,17 +1496,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1488,202 +1514,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="116">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>2026-10-03T21:50:24.795096Z</t>
+  </si>
+  <si>
+    <t>2026-10-04T01:59:44.402705Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1036,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1400,8 +1403,31 @@
         <v>355.83</v>
       </c>
     </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5">
+        <v>213.1305847167969</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2.708065271377563</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5">
+        <v>-2.33</v>
+      </c>
+      <c r="I16" s="5">
+        <v>350.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I15"/>
+  <autoFilter ref="A2:I16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1423,7 +1449,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1438,39 +1464,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1496,17 +1522,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1514,202 +1540,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="117">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>2026-10-04T01:59:44.402705Z</t>
+  </si>
+  <si>
+    <t>2026-10-04T08:47:05.526979Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1039,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1426,8 +1429,31 @@
         <v>350.2</v>
       </c>
     </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5">
+        <v>212.3018798828125</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0.6399621367454529</v>
+      </c>
+      <c r="G17" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H17" s="5">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="I17" s="5">
+        <v>377.31</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I16"/>
+  <autoFilter ref="A2:I17"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1449,7 +1475,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1464,39 +1490,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1522,17 +1548,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1540,202 +1566,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="118">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>2026-10-04T08:47:05.526979Z</t>
+  </si>
+  <si>
+    <t>2026-10-04T14:59:40.859860Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1042,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1452,8 +1455,33 @@
         <v>377.31</v>
       </c>
     </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="5">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5">
+        <v>208.3233337402344</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0.5173351168632507</v>
+      </c>
+      <c r="G18" s="5">
+        <v>5</v>
+      </c>
+      <c r="H18" s="5">
+        <v>-15.22</v>
+      </c>
+      <c r="I18" s="5">
+        <v>421.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I17"/>
+  <autoFilter ref="A2:I18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1475,7 +1503,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1490,39 +1518,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1548,17 +1576,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1566,202 +1594,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="119">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>2026-10-04T14:59:40.859860Z</t>
+  </si>
+  <si>
+    <t>2026-10-04T18:58:32.058621Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1045,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1480,8 +1483,31 @@
         <v>421.87</v>
       </c>
     </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5">
+        <v>136.8656616210938</v>
+      </c>
+      <c r="F19" s="5">
+        <v>110.4366989135742</v>
+      </c>
+      <c r="G19" s="5">
+        <v>5</v>
+      </c>
+      <c r="H19" s="5">
+        <v>-15</v>
+      </c>
+      <c r="I19" s="5">
+        <v>421.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I18"/>
+  <autoFilter ref="A2:I19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1503,7 +1529,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1518,39 +1544,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1576,17 +1602,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1594,202 +1620,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="120">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>2026-10-04T18:58:32.058621Z</t>
+  </si>
+  <si>
+    <t>2026-10-04T22:32:09.951034Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1048,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1506,8 +1509,31 @@
         <v>421.87</v>
       </c>
     </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5">
+        <v>36.58982849121094</v>
+      </c>
+      <c r="F20" s="5">
+        <v>6.298123359680176</v>
+      </c>
+      <c r="G20" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="H20" s="5">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="I20" s="5">
+        <v>487.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I19"/>
+  <autoFilter ref="A2:I20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1529,7 +1555,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1544,39 +1570,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1602,17 +1628,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1620,202 +1646,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="121">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>2026-10-04T22:32:09.951034Z</t>
+  </si>
+  <si>
+    <t>2026-10-05T01:17:02.635660Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1051,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1532,8 +1535,35 @@
         <v>487.6</v>
       </c>
     </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="5">
+        <v>-5.77</v>
+      </c>
+      <c r="D21" s="5">
+        <v>573.35</v>
+      </c>
+      <c r="E21" s="5">
+        <v>150.0973052978516</v>
+      </c>
+      <c r="F21" s="5">
+        <v>6.281254768371582</v>
+      </c>
+      <c r="G21" s="5">
+        <v>5</v>
+      </c>
+      <c r="H21" s="5">
+        <v>-7.47</v>
+      </c>
+      <c r="I21" s="5">
+        <v>493.97</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I20"/>
+  <autoFilter ref="A2:I21"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1555,7 +1585,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1570,39 +1600,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1628,17 +1658,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1646,202 +1676,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="122">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>2026-10-05T01:17:02.635660Z</t>
+  </si>
+  <si>
+    <t>2026-10-05T07:41:49.795159Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1054,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1562,8 +1565,35 @@
         <v>493.97</v>
       </c>
     </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="5">
+        <v>-5.26</v>
+      </c>
+      <c r="D22" s="5">
+        <v>545.39</v>
+      </c>
+      <c r="E22" s="5">
+        <v>327.9887084960938</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1.150961399078369</v>
+      </c>
+      <c r="G22" s="5">
+        <v>4.67</v>
+      </c>
+      <c r="H22" s="5">
+        <v>-7.2</v>
+      </c>
+      <c r="I22" s="5">
+        <v>480</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I21"/>
+  <autoFilter ref="A2:I22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1585,7 +1615,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1600,39 +1630,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1658,17 +1688,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1676,202 +1706,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>2026-10-05T07:41:49.795159Z</t>
+  </si>
+  <si>
+    <t>2026-10-05T16:30:05.859649Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1057,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1592,8 +1595,35 @@
         <v>480</v>
       </c>
     </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="5">
+        <v>-1.76</v>
+      </c>
+      <c r="D23" s="5">
+        <v>568.72</v>
+      </c>
+      <c r="E23" s="5">
+        <v>931.7824096679688</v>
+      </c>
+      <c r="F23" s="5">
+        <v>14.51318359375</v>
+      </c>
+      <c r="G23" s="5">
+        <v>3.33</v>
+      </c>
+      <c r="H23" s="5">
+        <v>-5.91</v>
+      </c>
+      <c r="I23" s="5">
+        <v>479.41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I22"/>
+  <autoFilter ref="A2:I23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1615,7 +1645,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1630,39 +1660,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1688,17 +1718,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1706,202 +1736,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>77</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="124">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>2026-10-05T16:30:05.859649Z</t>
+  </si>
+  <si>
+    <t>2026-10-05T22:55:28.374198Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1060,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1622,8 +1625,37 @@
         <v>479.41</v>
       </c>
     </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="5">
+        <v>3.67</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-0.77</v>
+      </c>
+      <c r="D24" s="5">
+        <v>531.74</v>
+      </c>
+      <c r="E24" s="5">
+        <v>875.169921875</v>
+      </c>
+      <c r="F24" s="5">
+        <v>14.43525218963623</v>
+      </c>
+      <c r="G24" s="5">
+        <v>3.33</v>
+      </c>
+      <c r="H24" s="5">
+        <v>-6.01</v>
+      </c>
+      <c r="I24" s="5">
+        <v>466.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I23"/>
+  <autoFilter ref="A2:I24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1645,7 +1677,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1660,39 +1692,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1718,17 +1750,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1736,202 +1768,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>2026-10-05T22:55:28.374198Z</t>
+  </si>
+  <si>
+    <t>2026-10-06T03:20:35.376443Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1063,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1654,8 +1657,31 @@
         <v>466.1</v>
       </c>
     </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5">
+        <v>2042.485961914062</v>
+      </c>
+      <c r="F25" s="5">
+        <v>3.033320665359497</v>
+      </c>
+      <c r="G25" s="5">
+        <v>3.33</v>
+      </c>
+      <c r="H25" s="5">
+        <v>-5.88</v>
+      </c>
+      <c r="I25" s="5">
+        <v>457.55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I24"/>
+  <autoFilter ref="A2:I25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1677,7 +1703,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1692,39 +1718,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1750,17 +1776,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1768,202 +1794,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>2026-10-06T03:20:35.376443Z</t>
+  </si>
+  <si>
+    <t>2026-10-06T10:47:34.949154Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1066,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1680,8 +1683,31 @@
         <v>457.55</v>
       </c>
     </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5">
+        <v>4196.95849609375</v>
+      </c>
+      <c r="F26" s="5">
+        <v>7.682991981506348</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="H26" s="5">
+        <v>-5.98</v>
+      </c>
+      <c r="I26" s="5">
+        <v>420.74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I25"/>
+  <autoFilter ref="A2:I26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1703,7 +1729,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1718,39 +1744,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1776,17 +1802,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1794,202 +1820,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>2026-10-06T10:47:34.949154Z</t>
+  </si>
+  <si>
+    <t>2026-10-06T17:26:05.072526Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1069,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1706,8 +1709,37 @@
         <v>420.74</v>
       </c>
     </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="D27" s="5">
+        <v>472.64</v>
+      </c>
+      <c r="E27" s="5">
+        <v>10198.453125</v>
+      </c>
+      <c r="F27" s="5">
+        <v>21.18011283874512</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H27" s="5">
+        <v>-4.47</v>
+      </c>
+      <c r="I27" s="5">
+        <v>395.53</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I26"/>
+  <autoFilter ref="A2:I27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1729,7 +1761,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1744,39 +1776,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1802,17 +1834,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1820,202 +1852,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="128">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>2026-10-06T17:26:05.072526Z</t>
+  </si>
+  <si>
+    <t>2026-10-06T21:54:30.626015Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1072,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1738,8 +1741,31 @@
         <v>395.53</v>
       </c>
     </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5">
+        <v>3988.219970703125</v>
+      </c>
+      <c r="F28" s="5">
+        <v>10.27724361419678</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H28" s="5">
+        <v>-4.33</v>
+      </c>
+      <c r="I28" s="5">
+        <v>395.53</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I27"/>
+  <autoFilter ref="A2:I28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1761,7 +1787,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1776,39 +1802,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1834,17 +1860,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1852,202 +1878,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>2026-10-06T21:54:30.626015Z</t>
+  </si>
+  <si>
+    <t>2026-10-07T01:49:21.340723Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1075,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1764,8 +1767,31 @@
         <v>395.53</v>
       </c>
     </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5">
+        <v>3436.310791015625</v>
+      </c>
+      <c r="F29" s="5">
+        <v>4.150707244873047</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5">
+        <v>-3.57</v>
+      </c>
+      <c r="I29" s="5">
+        <v>396.16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I28"/>
+  <autoFilter ref="A2:I29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1787,7 +1813,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1802,39 +1828,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1860,17 +1886,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1878,202 +1904,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>2026-10-07T01:49:21.340723Z</t>
+  </si>
+  <si>
+    <t>2026-10-07T09:15:20.020312Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1078,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1790,8 +1793,31 @@
         <v>396.16</v>
       </c>
     </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5">
+        <v>3562.845458984375</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1.098861217498779</v>
+      </c>
+      <c r="G30" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H30" s="5">
+        <v>-2.98</v>
+      </c>
+      <c r="I30" s="5">
+        <v>414.66</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I29"/>
+  <autoFilter ref="A2:I30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1813,7 +1839,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1828,39 +1854,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1886,17 +1912,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1904,202 +1930,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="131">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>2026-10-07T09:15:20.020312Z</t>
+  </si>
+  <si>
+    <t>2026-10-07T22:19:24.734909Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1081,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1816,8 +1819,31 @@
         <v>414.66</v>
       </c>
     </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5">
+        <v>6140.40869140625</v>
+      </c>
+      <c r="F31" s="5">
+        <v>10.57716464996338</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H31" s="5">
+        <v>-2.55</v>
+      </c>
+      <c r="I31" s="5">
+        <v>412.36</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I30"/>
+  <autoFilter ref="A2:I31"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1839,7 +1865,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1854,39 +1880,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1912,17 +1938,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1930,202 +1956,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>2026-10-07T22:19:24.734909Z</t>
+  </si>
+  <si>
+    <t>2026-10-08T02:16:35.354560Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1084,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1842,8 +1845,37 @@
         <v>412.36</v>
       </c>
     </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-2.91</v>
+      </c>
+      <c r="D32" s="5">
+        <v>369.2</v>
+      </c>
+      <c r="E32" s="5">
+        <v>4187.55810546875</v>
+      </c>
+      <c r="F32" s="5">
+        <v>4.250922679901123</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H32" s="5">
+        <v>-3.37</v>
+      </c>
+      <c r="I32" s="5">
+        <v>417.22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I31"/>
+  <autoFilter ref="A2:I32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1865,7 +1897,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1880,39 +1912,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1938,17 +1970,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1956,202 +1988,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="133">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>2026-10-08T02:16:35.354560Z</t>
+  </si>
+  <si>
+    <t>2026-10-08T09:28:18.531550Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1087,7 +1090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1874,8 +1877,31 @@
         <v>417.22</v>
       </c>
     </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5">
+        <v>3778.189453125</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0.4670102298259735</v>
+      </c>
+      <c r="G33" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H33" s="5">
+        <v>-2.91</v>
+      </c>
+      <c r="I33" s="5">
+        <v>417.22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I32"/>
+  <autoFilter ref="A2:I33"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1897,7 +1923,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1912,39 +1938,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1970,17 +1996,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1988,202 +2014,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="134">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>2026-10-08T09:28:18.531550Z</t>
+  </si>
+  <si>
+    <t>2026-10-08T16:57:32.595133Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1090,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1900,8 +1903,31 @@
         <v>417.22</v>
       </c>
     </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5">
+        <v>7005.22900390625</v>
+      </c>
+      <c r="F34" s="5">
+        <v>9.601882934570312</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H34" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="I34" s="5">
+        <v>409.84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I33"/>
+  <autoFilter ref="A2:I34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1923,7 +1949,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1938,39 +1964,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1996,17 +2022,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2014,202 +2040,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>2026-10-08T16:57:32.595133Z</t>
+  </si>
+  <si>
+    <t>2026-10-08T22:27:34.902927Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1093,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1926,8 +1929,31 @@
         <v>409.84</v>
       </c>
     </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5">
+        <v>265.8694763183594</v>
+      </c>
+      <c r="F35" s="5">
+        <v>25.64639091491699</v>
+      </c>
+      <c r="G35" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H35" s="5">
+        <v>-4.49</v>
+      </c>
+      <c r="I35" s="5">
+        <v>401.79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I34"/>
+  <autoFilter ref="A2:I35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1949,7 +1975,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1964,39 +1990,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2022,17 +2048,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2040,202 +2066,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="136">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>2026-10-08T22:27:34.902927Z</t>
+  </si>
+  <si>
+    <t>2026-10-09T02:34:30.036325Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1096,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1952,8 +1955,37 @@
         <v>401.79</v>
       </c>
     </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="D36" s="5">
+        <v>353.24</v>
+      </c>
+      <c r="E36" s="5">
+        <v>348.2550354003906</v>
+      </c>
+      <c r="F36" s="5">
+        <v>1.267776966094971</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5">
+        <v>-5.74</v>
+      </c>
+      <c r="I36" s="5">
+        <v>401.19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I35"/>
+  <autoFilter ref="A2:I36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1975,7 +2007,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1990,39 +2022,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2048,17 +2080,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2066,202 +2098,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>2026-10-09T02:34:30.036325Z</t>
+  </si>
+  <si>
+    <t>2026-10-09T09:38:17.661042Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1099,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1984,8 +1987,31 @@
         <v>401.19</v>
       </c>
     </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5">
+        <v>247.6436157226562</v>
+      </c>
+      <c r="F37" s="5">
+        <v>2.923715114593506</v>
+      </c>
+      <c r="G37" s="5">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5">
+        <v>-5.3</v>
+      </c>
+      <c r="I37" s="5">
+        <v>401.19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I36"/>
+  <autoFilter ref="A2:I37"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2007,7 +2033,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2022,39 +2048,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2080,17 +2106,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2098,202 +2124,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="138">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>2026-10-09T09:38:17.661042Z</t>
+  </si>
+  <si>
+    <t>2026-10-09T16:33:54.399632Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1102,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2010,8 +2013,31 @@
         <v>401.19</v>
       </c>
     </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5">
+        <v>245.1904449462891</v>
+      </c>
+      <c r="F38" s="5">
+        <v>4.083504199981689</v>
+      </c>
+      <c r="G38" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H38" s="5">
+        <v>-6.73</v>
+      </c>
+      <c r="I38" s="5">
+        <v>408.95</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I37"/>
+  <autoFilter ref="A2:I38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2033,7 +2059,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2048,39 +2074,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2106,17 +2132,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2124,202 +2150,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="139">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>2026-10-09T16:33:54.399632Z</t>
+  </si>
+  <si>
+    <t>2026-10-09T21:17:40.885294Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1105,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2036,8 +2039,31 @@
         <v>408.95</v>
       </c>
     </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5">
+        <v>274.2161254882812</v>
+      </c>
+      <c r="F39" s="5">
+        <v>10.37603092193604</v>
+      </c>
+      <c r="G39" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H39" s="5">
+        <v>-4.23</v>
+      </c>
+      <c r="I39" s="5">
+        <v>414.85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I38"/>
+  <autoFilter ref="A2:I39"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2059,7 +2085,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2074,39 +2100,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2132,17 +2158,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2150,202 +2176,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="140">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>2026-10-09T21:17:40.885294Z</t>
+  </si>
+  <si>
+    <t>2026-10-10T01:33:10.293286Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1108,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2062,8 +2065,31 @@
         <v>414.85</v>
       </c>
     </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="5">
+        <v>48.60914993286133</v>
+      </c>
+      <c r="F40" s="5">
+        <v>3.835264205932617</v>
+      </c>
+      <c r="G40" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H40" s="5">
+        <v>-4.16</v>
+      </c>
+      <c r="I40" s="5">
+        <v>414.85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I39"/>
+  <autoFilter ref="A2:I40"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2085,7 +2111,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2100,39 +2126,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2158,17 +2184,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2176,202 +2202,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="141">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>2026-10-10T01:33:10.293286Z</t>
+  </si>
+  <si>
+    <t>2026-10-10T07:45:05.797476Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1111,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2088,8 +2091,31 @@
         <v>414.85</v>
       </c>
     </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="5">
+        <v>204.8112640380859</v>
+      </c>
+      <c r="F41" s="5">
+        <v>32.34529876708984</v>
+      </c>
+      <c r="G41" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="H41" s="5">
+        <v>-4.34</v>
+      </c>
+      <c r="I41" s="5">
+        <v>415.85</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I40"/>
+  <autoFilter ref="A2:I41"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2111,7 +2137,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2126,39 +2152,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2184,17 +2210,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2202,202 +2228,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="142">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>2026-10-10T07:45:05.797476Z</t>
+  </si>
+  <si>
+    <t>2026-10-10T14:44:02.158228Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1114,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2114,8 +2117,31 @@
         <v>415.85</v>
       </c>
     </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="5">
+        <v>1369.292846679688</v>
+      </c>
+      <c r="F42" s="5">
+        <v>40.02803802490234</v>
+      </c>
+      <c r="G42" s="5">
+        <v>3</v>
+      </c>
+      <c r="H42" s="5">
+        <v>-5.28</v>
+      </c>
+      <c r="I42" s="5">
+        <v>456.12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I41"/>
+  <autoFilter ref="A2:I42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2137,7 +2163,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2152,39 +2178,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2210,17 +2236,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2228,202 +2254,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>2026-10-10T14:44:02.158228Z</t>
+  </si>
+  <si>
+    <t>2026-10-10T18:54:06.026506Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1117,7 +1120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2140,8 +2143,35 @@
         <v>456.12</v>
       </c>
     </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="5">
+        <v>-18.53</v>
+      </c>
+      <c r="D43" s="5">
+        <v>712.9</v>
+      </c>
+      <c r="E43" s="5">
+        <v>203.1054840087891</v>
+      </c>
+      <c r="F43" s="5">
+        <v>4.406575679779053</v>
+      </c>
+      <c r="G43" s="5">
+        <v>3.67</v>
+      </c>
+      <c r="H43" s="5">
+        <v>-20.51</v>
+      </c>
+      <c r="I43" s="5">
+        <v>539.67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I42"/>
+  <autoFilter ref="A2:I43"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2163,7 +2193,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2178,39 +2208,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2236,17 +2266,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2254,202 +2284,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>2026-10-10T18:54:06.026506Z</t>
+  </si>
+  <si>
+    <t>2026-10-10T22:56:30.403154Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1120,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2170,8 +2173,37 @@
         <v>539.67</v>
       </c>
     </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="D44" s="5">
+        <v>767.89</v>
+      </c>
+      <c r="E44" s="5">
+        <v>214.7877044677734</v>
+      </c>
+      <c r="F44" s="5">
+        <v>79.99644470214844</v>
+      </c>
+      <c r="G44" s="5">
+        <v>7</v>
+      </c>
+      <c r="H44" s="5">
+        <v>-22.2</v>
+      </c>
+      <c r="I44" s="5">
+        <v>688.96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I43"/>
+  <autoFilter ref="A2:I44"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2193,7 +2225,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2208,39 +2240,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2266,17 +2298,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2284,202 +2316,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="145">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -255,6 +255,9 @@
   </si>
   <si>
     <t>2026-10-10T22:56:30.403154Z</t>
+  </si>
+  <si>
+    <t>2026-10-11T02:11:24.055159Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1123,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2202,8 +2205,31 @@
         <v>688.96</v>
       </c>
     </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5">
+        <v>195.3080444335938</v>
+      </c>
+      <c r="F45" s="5">
+        <v>154.32666015625</v>
+      </c>
+      <c r="G45" s="5">
+        <v>7</v>
+      </c>
+      <c r="H45" s="5">
+        <v>-22.2</v>
+      </c>
+      <c r="I45" s="5">
+        <v>688.96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I44"/>
+  <autoFilter ref="A2:I45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2225,7 +2251,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2240,39 +2266,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2298,17 +2324,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2316,202 +2342,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>2026-10-11T02:11:24.055159Z</t>
+  </si>
+  <si>
+    <t>2026-10-11T09:18:34.017408Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1126,7 +1129,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2228,8 +2231,31 @@
         <v>688.96</v>
       </c>
     </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5">
+        <v>213.0343933105469</v>
+      </c>
+      <c r="F46" s="5">
+        <v>182.9046020507812</v>
+      </c>
+      <c r="G46" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="H46" s="5">
+        <v>-4.46</v>
+      </c>
+      <c r="I46" s="5">
+        <v>570.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I45"/>
+  <autoFilter ref="A2:I46"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2251,7 +2277,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2266,39 +2292,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2324,17 +2350,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2342,202 +2368,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="147">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>2026-10-11T09:18:34.017408Z</t>
+  </si>
+  <si>
+    <t>2026-10-11T15:58:07.181580Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1129,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2254,8 +2257,31 @@
         <v>570.83</v>
       </c>
     </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5">
+        <v>277.8025817871094</v>
+      </c>
+      <c r="F47" s="5">
+        <v>24.90026473999023</v>
+      </c>
+      <c r="G47" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="H47" s="5">
+        <v>-5.5</v>
+      </c>
+      <c r="I47" s="5">
+        <v>553.27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I46"/>
+  <autoFilter ref="A2:I47"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2277,7 +2303,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2292,39 +2318,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2350,17 +2376,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2368,202 +2394,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="148">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>2026-10-11T15:58:07.181580Z</t>
+  </si>
+  <si>
+    <t>2026-10-11T20:35:20.438679Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1132,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2280,8 +2283,37 @@
         <v>553.27</v>
       </c>
     </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="C48" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="D48" s="5">
+        <v>552.84</v>
+      </c>
+      <c r="E48" s="5">
+        <v>118.1806182861328</v>
+      </c>
+      <c r="F48" s="5">
+        <v>39.57709884643555</v>
+      </c>
+      <c r="G48" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H48" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="I48" s="5">
+        <v>530.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I47"/>
+  <autoFilter ref="A2:I48"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2303,7 +2335,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2318,39 +2350,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2376,17 +2408,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2394,202 +2426,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="149">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>2026-10-11T20:35:20.438679Z</t>
+  </si>
+  <si>
+    <t>2026-10-11T23:59:58.243614Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1135,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2312,8 +2315,31 @@
         <v>530.75</v>
       </c>
     </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5">
+        <v>104.0260543823242</v>
+      </c>
+      <c r="F49" s="5">
+        <v>26.50642967224121</v>
+      </c>
+      <c r="G49" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="H49" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="I49" s="5">
+        <v>523.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I48"/>
+  <autoFilter ref="A2:I49"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2335,7 +2361,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2350,39 +2376,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2408,17 +2434,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2426,202 +2452,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="150">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>2026-10-11T23:59:58.243614Z</t>
+  </si>
+  <si>
+    <t>2026-10-12T06:31:28.569790Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1138,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2338,8 +2341,31 @@
         <v>523.02</v>
       </c>
     </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5">
+        <v>155.2315673828125</v>
+      </c>
+      <c r="F50" s="5">
+        <v>12.57616329193115</v>
+      </c>
+      <c r="G50" s="5">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5">
+        <v>-3.57</v>
+      </c>
+      <c r="I50" s="5">
+        <v>493.27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I49"/>
+  <autoFilter ref="A2:I50"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2361,7 +2387,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2376,39 +2402,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2434,17 +2460,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2452,202 +2478,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -13,15 +13,15 @@
     <sheet name="Method_Legend" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="161">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -101,6 +101,39 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-10-12T13:00:00Z</t>
+  </si>
+  <si>
+    <t>GOES-18</t>
+  </si>
+  <si>
+    <t>product/data</t>
+  </si>
+  <si>
+    <t>anomaly/outage</t>
+  </si>
+  <si>
+    <t>PRODUCT_DATA</t>
+  </si>
+  <si>
+    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: Correction: GOES-18, 19 - GOES-18, 19 products delivered to PDA Issued: Oct 12, 2026 1300Z</t>
+  </si>
+  <si>
+    <t>Temporal association only; causality NOT established.</t>
+  </si>
+  <si>
+    <t>NOAA OSPO satellite messages</t>
+  </si>
+  <si>
+    <t>2026-10-12T11:47:00Z</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: GOES-18, 19 - products delivered to AWIPS, GRB, PDA, SWPC -Issued: Oct 12, 2026 1147Z</t>
+  </si>
+  <si>
     <t>Hourly GEO Space Environment Log — 2026-10</t>
   </si>
   <si>
@@ -275,6 +308,9 @@
     <t>2026-10-12T06:31:28.569790Z</t>
   </si>
   <si>
+    <t>2026-10-12T16:14:36.541458Z</t>
+  </si>
+  <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
   </si>
   <si>
@@ -432,9 +468,6 @@
   </si>
   <si>
     <t>Instrument-level public alert</t>
-  </si>
-  <si>
-    <t>PRODUCT_DATA</t>
   </si>
   <si>
     <t>#E6A84C</t>
@@ -480,7 +513,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +540,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF101820"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -554,6 +595,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6A84C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFF8C42"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -591,12 +638,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFB14E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6A84C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -664,7 +705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -678,19 +719,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -987,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1129,8 +1173,138 @@
         <v>25</v>
       </c>
     </row>
+    <row r="4" spans="1:24">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="O4" s="6">
+        <v>608.65</v>
+      </c>
+      <c r="P4" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="R4" s="6">
+        <v>614.65</v>
+      </c>
+      <c r="S4" s="6">
+        <v>7</v>
+      </c>
+      <c r="T4" s="6">
+        <v>-29.83</v>
+      </c>
+      <c r="U4" s="6">
+        <v>904.2</v>
+      </c>
+      <c r="V4" s="6">
+        <v>94.2</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6">
+        <v>1.66</v>
+      </c>
+      <c r="J5" s="6">
+        <v>469.76</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="N5" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="O5" s="6">
+        <v>608.65</v>
+      </c>
+      <c r="P5" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="R5" s="6">
+        <v>618.9400000000001</v>
+      </c>
+      <c r="S5" s="6">
+        <v>7</v>
+      </c>
+      <c r="T5" s="6">
+        <v>-29.83</v>
+      </c>
+      <c r="U5" s="6">
+        <v>904.2</v>
+      </c>
+      <c r="V5" s="6">
+        <v>94.2</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:X3"/>
+  <autoFilter ref="A3:X5"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -1141,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1150,7 +1324,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1163,1209 +1337,1232 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="5">
+        <v>47</v>
+      </c>
+      <c r="B3" s="6">
         <v>0.67</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>-0.4</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="6">
         <v>285.23</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="6">
         <v>452.5343627929688</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="6">
         <v>2.319164037704468</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <v>1.33</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>-9.5</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <v>534.89</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="5">
+      <c r="E4" s="6">
         <v>339.3909301757812</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>0.5627515316009521</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <v>1.33</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>-9.5</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="6">
         <v>534.89</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5">
+      <c r="E5" s="6">
         <v>2060.4169921875</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <v>6.204731941223145</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="6">
         <v>1.33</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>-8.859999999999999</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="6">
         <v>531.38</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="5">
+      <c r="E6" s="6">
         <v>628.7714233398438</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="6">
         <v>21.36655426025391</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <v>1.67</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>-11.68</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="6">
         <v>535.8200000000001</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="5">
+      <c r="E7" s="6">
         <v>156.4220275878906</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <v>3.230470180511475</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="6">
         <v>1.67</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>-11.68</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="6">
         <v>535.8200000000001</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="5">
+      <c r="E8" s="6">
         <v>173.2319641113281</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="6">
         <v>0.7507917284965515</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <v>2.33</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>-11.1</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="6">
         <v>555.33</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5">
+      <c r="E9" s="6">
         <v>651.74267578125</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>1.206049799919128</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>0.67</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="6">
         <v>-3.23</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="6">
         <v>528.34</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="5">
+        <v>54</v>
+      </c>
+      <c r="B10" s="6">
         <v>0.67</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>-0.41</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="6">
         <v>283.88</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="6">
         <v>342.2538452148438</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <v>7.730380535125732</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <v>0.67</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <v>-3.31</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="6">
         <v>386.9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="5">
+      <c r="E11" s="6">
         <v>303.5421447753906</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="6">
         <v>2.036928415298462</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="6">
         <v>0.67</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="6">
         <v>-2.66</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="6">
         <v>374.03</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5">
+      <c r="E12" s="6">
         <v>118.4067153930664</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>0.7667706608772278</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>2.33</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>-4.19</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="6">
         <v>375.81</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="5">
+      <c r="E13" s="6">
         <v>472.7425231933594</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="6">
         <v>0.6435344219207764</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="6">
         <v>2.67</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="6">
         <v>-5.87</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="6">
         <v>365.84</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="5">
+      <c r="C14" s="6">
         <v>2.28</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="6">
         <v>284.71</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="6">
         <v>141.0826568603516</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="6">
         <v>5.628716945648193</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="6">
         <v>1.67</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="6">
         <v>-2.48</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="6">
         <v>355.83</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="5">
+      <c r="E15" s="6">
         <v>228.9217071533203</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <v>8.886663436889648</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="6">
         <v>1.33</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <v>-2.34</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="6">
         <v>355.83</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="5">
+      <c r="E16" s="6">
         <v>213.1305847167969</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <v>2.708065271377563</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="6">
         <v>1</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <v>-2.33</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="6">
         <v>350.2</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="5">
+      <c r="E17" s="6">
         <v>212.3018798828125</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <v>0.6399621367454529</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="6">
         <v>2.33</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <v>-9.300000000000001</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="6">
         <v>377.31</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="5">
+        <v>62</v>
+      </c>
+      <c r="B18" s="6">
         <v>5</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="5">
+      <c r="E18" s="6">
         <v>208.3233337402344</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="6">
         <v>0.5173351168632507</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="6">
         <v>5</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="6">
         <v>-15.22</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="6">
         <v>421.87</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="5">
+      <c r="E19" s="6">
         <v>136.8656616210938</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="6">
         <v>110.4366989135742</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="6">
         <v>5</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="6">
         <v>-15</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="6">
         <v>421.87</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="5">
+      <c r="E20" s="6">
         <v>36.58982849121094</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="6">
         <v>6.298123359680176</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="6">
         <v>4.33</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="6">
         <v>-8.539999999999999</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="6">
         <v>487.6</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <v>-5.77</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="6">
         <v>573.35</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6">
         <v>150.0973052978516</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <v>6.281254768371582</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="6">
         <v>5</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <v>-7.47</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="6">
         <v>493.97</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <v>-5.26</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="6">
         <v>545.39</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="6">
         <v>327.9887084960938</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="6">
         <v>1.150961399078369</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="6">
         <v>4.67</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="6">
         <v>-7.2</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="6">
         <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
         <v>-1.76</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="6">
         <v>568.72</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="6">
         <v>931.7824096679688</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="6">
         <v>14.51318359375</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="6">
         <v>3.33</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>-5.91</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="6">
         <v>479.41</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="5">
+        <v>68</v>
+      </c>
+      <c r="B24" s="6">
         <v>3.67</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <v>-0.77</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="6">
         <v>531.74</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="6">
         <v>875.169921875</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="6">
         <v>14.43525218963623</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="6">
         <v>3.33</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>-6.01</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="6">
         <v>466.1</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="E25" s="5">
+      <c r="E25" s="6">
         <v>2042.485961914062</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="6">
         <v>3.033320665359497</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="6">
         <v>3.33</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="6">
         <v>-5.88</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="6">
         <v>457.55</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="5">
+      <c r="E26" s="6">
         <v>4196.95849609375</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="6">
         <v>7.682991981506348</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="6">
         <v>2.67</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="6">
         <v>-5.98</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="6">
         <v>420.74</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="5">
+        <v>71</v>
+      </c>
+      <c r="B27" s="6">
         <v>2.67</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="6">
         <v>0.91</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="6">
         <v>472.64</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="6">
         <v>10198.453125</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="6">
         <v>21.18011283874512</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="6">
         <v>2.33</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="6">
         <v>-4.47</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="6">
         <v>395.53</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="E28" s="5">
+      <c r="E28" s="6">
         <v>3988.219970703125</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="6">
         <v>10.27724361419678</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="6">
         <v>2.33</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="6">
         <v>-4.33</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="6">
         <v>395.53</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
-      <c r="E29" s="5">
+      <c r="E29" s="6">
         <v>3436.310791015625</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="6">
         <v>4.150707244873047</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="6">
         <v>2</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="6">
         <v>-3.57</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="6">
         <v>396.16</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
-      <c r="E30" s="5">
+      <c r="E30" s="6">
         <v>3562.845458984375</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="6">
         <v>1.098861217498779</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="6">
         <v>1.67</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="6">
         <v>-2.98</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="6">
         <v>414.66</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
-      <c r="E31" s="5">
+      <c r="E31" s="6">
         <v>6140.40869140625</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="6">
         <v>10.57716464996338</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="6">
         <v>1.67</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="6">
         <v>-2.55</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="6">
         <v>412.36</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="5">
+        <v>76</v>
+      </c>
+      <c r="B32" s="6">
         <v>1</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="6">
         <v>-2.91</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="6">
         <v>369.2</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="6">
         <v>4187.55810546875</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="6">
         <v>4.250922679901123</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="6">
         <v>1.67</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="6">
         <v>-3.37</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="6">
         <v>417.22</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="5">
+      <c r="E33" s="6">
         <v>3778.189453125</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="6">
         <v>0.4670102298259735</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="6">
         <v>1.67</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="6">
         <v>-2.91</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="6">
         <v>417.22</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
-      <c r="E34" s="5">
+      <c r="E34" s="6">
         <v>7005.22900390625</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="6">
         <v>9.601882934570312</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="6">
         <v>1.67</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="6">
         <v>-2.68</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="6">
         <v>409.84</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
-      <c r="E35" s="5">
+      <c r="E35" s="6">
         <v>265.8694763183594</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="6">
         <v>25.64639091491699</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="6">
         <v>1.67</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="6">
         <v>-4.49</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="6">
         <v>401.79</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="5">
+        <v>80</v>
+      </c>
+      <c r="B36" s="6">
         <v>1.33</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="6">
         <v>1.51</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="6">
         <v>353.24</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="6">
         <v>348.2550354003906</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="6">
         <v>1.267776966094971</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="6">
         <v>2</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="6">
         <v>-5.74</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="6">
         <v>401.19</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
-      <c r="E37" s="5">
+      <c r="E37" s="6">
         <v>247.6436157226562</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="6">
         <v>2.923715114593506</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="6">
         <v>2</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="6">
         <v>-5.3</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="6">
         <v>401.19</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
-      <c r="E38" s="5">
+      <c r="E38" s="6">
         <v>245.1904449462891</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="6">
         <v>4.083504199981689</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="6">
         <v>2.33</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="6">
         <v>-6.73</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="6">
         <v>408.95</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
-      <c r="E39" s="5">
+      <c r="E39" s="6">
         <v>274.2161254882812</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="6">
         <v>10.37603092193604</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="6">
         <v>2.33</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="6">
         <v>-4.23</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="6">
         <v>414.85</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="5">
+      <c r="E40" s="6">
         <v>48.60914993286133</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="6">
         <v>3.835264205932617</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="6">
         <v>2.33</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="6">
         <v>-4.16</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="6">
         <v>414.85</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
-      <c r="E41" s="5">
+      <c r="E41" s="6">
         <v>204.8112640380859</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="6">
         <v>32.34529876708984</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="6">
         <v>2.67</v>
       </c>
-      <c r="H41" s="5">
+      <c r="H41" s="6">
         <v>-4.34</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="6">
         <v>415.85</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
-      <c r="E42" s="5">
+      <c r="E42" s="6">
         <v>1369.292846679688</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="6">
         <v>40.02803802490234</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="6">
         <v>3</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H42" s="6">
         <v>-5.28</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="6">
         <v>456.12</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B43" s="4"/>
-      <c r="C43" s="5">
+      <c r="C43" s="6">
         <v>-18.53</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="6">
         <v>712.9</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="6">
         <v>203.1054840087891</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="6">
         <v>4.406575679779053</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="6">
         <v>3.67</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="6">
         <v>-20.51</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="6">
         <v>539.67</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="5">
+        <v>88</v>
+      </c>
+      <c r="B44" s="6">
         <v>6.67</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="6">
         <v>1.7</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="6">
         <v>767.89</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="6">
         <v>214.7877044677734</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="6">
         <v>79.99644470214844</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="6">
         <v>7</v>
       </c>
-      <c r="H44" s="5">
+      <c r="H44" s="6">
         <v>-22.2</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="6">
         <v>688.96</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
-      <c r="E45" s="5">
+      <c r="E45" s="6">
         <v>195.3080444335938</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="6">
         <v>154.32666015625</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="6">
         <v>7</v>
       </c>
-      <c r="H45" s="5">
+      <c r="H45" s="6">
         <v>-22.2</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="6">
         <v>688.96</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
-      <c r="E46" s="5">
+      <c r="E46" s="6">
         <v>213.0343933105469</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="6">
         <v>182.9046020507812</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="6">
         <v>4.33</v>
       </c>
-      <c r="H46" s="5">
+      <c r="H46" s="6">
         <v>-4.46</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="6">
         <v>570.83</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
-      <c r="E47" s="5">
+      <c r="E47" s="6">
         <v>277.8025817871094</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="6">
         <v>24.90026473999023</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="6">
         <v>2.67</v>
       </c>
-      <c r="H47" s="5">
+      <c r="H47" s="6">
         <v>-5.5</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="6">
         <v>553.27</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48" s="5">
+        <v>92</v>
+      </c>
+      <c r="B48" s="6">
         <v>2.33</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="6">
         <v>0.83</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="6">
         <v>552.84</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="6">
         <v>118.1806182861328</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="6">
         <v>39.57709884643555</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="6">
         <v>2.33</v>
       </c>
-      <c r="H48" s="5">
+      <c r="H48" s="6">
         <v>-3.19</v>
       </c>
-      <c r="I48" s="5">
+      <c r="I48" s="6">
         <v>530.75</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
-      <c r="E49" s="5">
+      <c r="E49" s="6">
         <v>104.0260543823242</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="6">
         <v>26.50642967224121</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="6">
         <v>2.33</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H49" s="6">
         <v>-3.19</v>
       </c>
-      <c r="I49" s="5">
+      <c r="I49" s="6">
         <v>523.02</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="4" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
-      <c r="E50" s="5">
+      <c r="E50" s="6">
         <v>155.2315673828125</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="6">
         <v>12.57616329193115</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="6">
         <v>2</v>
       </c>
-      <c r="H50" s="5">
+      <c r="H50" s="6">
         <v>-3.57</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="6">
         <v>493.27</v>
       </c>
     </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="6">
+        <v>247.0723724365234</v>
+      </c>
+      <c r="F51" s="6">
+        <v>37.83306503295898</v>
+      </c>
+      <c r="G51" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H51" s="6">
+        <v>-4.12</v>
+      </c>
+      <c r="I51" s="6">
+        <v>490.27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I50"/>
+  <autoFilter ref="A2:I51"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2387,7 +2584,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2402,39 +2599,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2460,17 +2657,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2478,202 +2675,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>117</v>
+        <v>128</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>120</v>
+        <v>131</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>123</v>
+        <v>134</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>126</v>
+        <v>137</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>129</v>
+        <v>140</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>141</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>132</v>
+        <v>143</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>135</v>
+        <v>146</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>138</v>
+        <v>30</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>141</v>
+        <v>151</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="15" t="s">
-        <v>144</v>
+      <c r="A24" s="16" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="15" t="s">
-        <v>145</v>
+      <c r="A25" s="16" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="15" t="s">
-        <v>146</v>
+      <c r="A26" s="16" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="15" t="s">
-        <v>147</v>
+      <c r="A27" s="16" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="15" t="s">
-        <v>148</v>
+      <c r="A28" s="16" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="15" t="s">
-        <v>149</v>
+      <c r="A29" s="16" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="162">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>2026-10-12T16:14:36.541458Z</t>
+  </si>
+  <si>
+    <t>2026-10-12T23:14:09.229353Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1195,14 +1198,22 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="H4" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="I4" s="6">
+        <v>3.25</v>
+      </c>
+      <c r="J4" s="6">
+        <v>460.8</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
+      <c r="M4" s="6">
+        <v>1.33</v>
+      </c>
       <c r="N4" s="6">
-        <v>-1.12</v>
+        <v>-1.08</v>
       </c>
       <c r="O4" s="6">
         <v>608.65</v>
@@ -1214,7 +1225,7 @@
         <v>-4.35</v>
       </c>
       <c r="R4" s="6">
-        <v>614.65</v>
+        <v>631.91</v>
       </c>
       <c r="S4" s="6">
         <v>7</v>
@@ -1257,12 +1268,14 @@
       <c r="G5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="6">
+        <v>0.67</v>
+      </c>
       <c r="I5" s="6">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="J5" s="6">
-        <v>469.76</v>
+        <v>460.6</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -1270,7 +1283,7 @@
         <v>3.33</v>
       </c>
       <c r="N5" s="6">
-        <v>-3.67</v>
+        <v>-3.01</v>
       </c>
       <c r="O5" s="6">
         <v>608.65</v>
@@ -1282,7 +1295,7 @@
         <v>-4.35</v>
       </c>
       <c r="R5" s="6">
-        <v>618.9400000000001</v>
+        <v>631.91</v>
       </c>
       <c r="S5" s="6">
         <v>7</v>
@@ -1315,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2561,8 +2574,35 @@
         <v>490.27</v>
       </c>
     </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="6">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>5.33</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6">
+        <v>185.5925903320312</v>
+      </c>
+      <c r="F52" s="6">
+        <v>63.68589401245117</v>
+      </c>
+      <c r="G52" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="H52" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="I52" s="6">
+        <v>526.52</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I51"/>
+  <autoFilter ref="A2:I52"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2584,7 +2624,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2599,39 +2639,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2657,17 +2697,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2675,145 +2715,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2821,56 +2861,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="163">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>2026-10-12T23:14:09.229353Z</t>
+  </si>
+  <si>
+    <t>2026-10-13T03:52:37.276744Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1328,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2601,8 +2604,31 @@
         <v>526.52</v>
       </c>
     </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6">
+        <v>231.3461456298828</v>
+      </c>
+      <c r="F53" s="6">
+        <v>9.17764949798584</v>
+      </c>
+      <c r="G53" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="H53" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="I53" s="6">
+        <v>526.52</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I52"/>
+  <autoFilter ref="A2:I53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2624,7 +2650,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2639,39 +2665,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2697,17 +2723,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2715,145 +2741,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2861,56 +2887,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="164">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>2026-10-13T03:52:37.276744Z</t>
+  </si>
+  <si>
+    <t>2026-10-13T12:10:43.623035Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1208,7 +1211,7 @@
         <v>3.25</v>
       </c>
       <c r="J4" s="6">
-        <v>460.8</v>
+        <v>469.21</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -1216,7 +1219,7 @@
         <v>1.33</v>
       </c>
       <c r="N4" s="6">
-        <v>-1.08</v>
+        <v>-1.12</v>
       </c>
       <c r="O4" s="6">
         <v>608.65</v>
@@ -1275,7 +1278,7 @@
         <v>0.67</v>
       </c>
       <c r="I5" s="6">
-        <v>2.6</v>
+        <v>0.83</v>
       </c>
       <c r="J5" s="6">
         <v>460.6</v>
@@ -1331,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2627,8 +2630,31 @@
         <v>526.52</v>
       </c>
     </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6">
+        <v>156.1480407714844</v>
+      </c>
+      <c r="F54" s="6">
+        <v>3.553812026977539</v>
+      </c>
+      <c r="G54" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H54" s="6">
+        <v>-4.26</v>
+      </c>
+      <c r="I54" s="6">
+        <v>547.89</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I53"/>
+  <autoFilter ref="A2:I54"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2650,7 +2676,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2665,39 +2691,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2723,17 +2749,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2741,145 +2767,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2887,56 +2913,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="165">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>2026-10-13T12:10:43.623035Z</t>
+  </si>
+  <si>
+    <t>2026-10-13T19:32:49.636308Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1334,7 +1337,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2653,8 +2656,31 @@
         <v>547.89</v>
       </c>
     </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="6">
+        <v>168.7785339355469</v>
+      </c>
+      <c r="F55" s="6">
+        <v>7.749381542205811</v>
+      </c>
+      <c r="G55" s="6">
+        <v>3</v>
+      </c>
+      <c r="H55" s="6">
+        <v>-4.56</v>
+      </c>
+      <c r="I55" s="6">
+        <v>587.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I54"/>
+  <autoFilter ref="A2:I55"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2676,7 +2702,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2691,39 +2717,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2749,17 +2775,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2767,145 +2793,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2913,56 +2939,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="166">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>2026-10-13T19:32:49.636308Z</t>
+  </si>
+  <si>
+    <t>2026-10-13T23:39:19.601848Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1337,7 +1340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2679,8 +2682,31 @@
         <v>587.87</v>
       </c>
     </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="6">
+        <v>59.9532356262207</v>
+      </c>
+      <c r="F56" s="6">
+        <v>1.593339085578918</v>
+      </c>
+      <c r="G56" s="6">
+        <v>3</v>
+      </c>
+      <c r="H56" s="6">
+        <v>-5.05</v>
+      </c>
+      <c r="I56" s="6">
+        <v>587.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I55"/>
+  <autoFilter ref="A2:I56"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2702,7 +2728,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2717,39 +2743,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2775,17 +2801,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2793,145 +2819,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2939,56 +2965,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="167">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>2026-10-13T23:39:19.601848Z</t>
+  </si>
+  <si>
+    <t>2026-10-14T02:10:29.015505Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1340,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2705,8 +2708,31 @@
         <v>587.87</v>
       </c>
     </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="6">
+        <v>146.17431640625</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0.7570022344589233</v>
+      </c>
+      <c r="G57" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="H57" s="6">
+        <v>-3.31</v>
+      </c>
+      <c r="I57" s="6">
+        <v>641.5700000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I56"/>
+  <autoFilter ref="A2:I57"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2728,7 +2754,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2743,39 +2769,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2801,17 +2827,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2819,145 +2845,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2965,56 +2991,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="168">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>2026-10-14T02:10:29.015505Z</t>
+  </si>
+  <si>
+    <t>2026-10-14T08:01:38.047485Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1343,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2731,8 +2734,31 @@
         <v>641.5700000000001</v>
       </c>
     </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="6">
+        <v>193.5009765625</v>
+      </c>
+      <c r="F58" s="6">
+        <v>0.7793199419975281</v>
+      </c>
+      <c r="G58" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H58" s="6">
+        <v>-3.02</v>
+      </c>
+      <c r="I58" s="6">
+        <v>610.4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I57"/>
+  <autoFilter ref="A2:I58"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2754,7 +2780,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2769,39 +2795,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2827,17 +2853,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2845,145 +2871,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2991,56 +3017,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="169">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>2026-10-14T08:01:38.047485Z</t>
+  </si>
+  <si>
+    <t>2026-10-14T14:02:11.985740Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1346,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2757,8 +2760,31 @@
         <v>610.4</v>
       </c>
     </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="6">
+        <v>1.225303173065186</v>
+      </c>
+      <c r="G59" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H59" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="I59" s="6">
+        <v>563.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I58"/>
+  <autoFilter ref="A2:I59"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2780,7 +2806,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2795,39 +2821,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2853,17 +2879,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2871,145 +2897,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3017,56 +3043,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="170">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>2026-10-14T14:02:11.985740Z</t>
+  </si>
+  <si>
+    <t>2026-10-14T18:53:54.436149Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1349,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2783,8 +2786,35 @@
         <v>563.83</v>
       </c>
     </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="D60" s="6">
+        <v>525.67</v>
+      </c>
+      <c r="E60" s="6">
+        <v>252.7300415039062</v>
+      </c>
+      <c r="F60" s="6">
+        <v>14.51102066040039</v>
+      </c>
+      <c r="G60" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H60" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="I60" s="6">
+        <v>544.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I59"/>
+  <autoFilter ref="A2:I60"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2806,7 +2836,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2821,39 +2851,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2879,17 +2909,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2897,145 +2927,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3043,56 +3073,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="171">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>2026-10-14T18:53:54.436149Z</t>
+  </si>
+  <si>
+    <t>2026-10-14T22:41:37.767315Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1352,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2813,8 +2816,29 @@
         <v>544.75</v>
       </c>
     </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="6">
+        <v>115.8916625976562</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H61" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="I61" s="6">
+        <v>541.54</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I60"/>
+  <autoFilter ref="A2:I61"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2836,7 +2860,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2851,39 +2875,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2909,17 +2933,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2927,145 +2951,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3073,56 +3097,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="172">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>2026-10-14T22:41:37.767315Z</t>
+  </si>
+  <si>
+    <t>2026-10-15T00:51:43.748629Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1355,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2837,8 +2840,31 @@
         <v>541.54</v>
       </c>
     </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="6">
+        <v>78.74021148681641</v>
+      </c>
+      <c r="F62" s="6">
+        <v>1.902230381965637</v>
+      </c>
+      <c r="G62" s="6">
+        <v>3</v>
+      </c>
+      <c r="H62" s="6">
+        <v>-3.31</v>
+      </c>
+      <c r="I62" s="6">
+        <v>554.0700000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I61"/>
+  <autoFilter ref="A2:I62"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2860,7 +2886,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2875,39 +2901,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2933,17 +2959,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2951,145 +2977,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3097,56 +3123,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="173">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>2026-10-15T00:51:43.748629Z</t>
+  </si>
+  <si>
+    <t>2026-10-15T06:27:00.786538Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1358,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2863,8 +2866,35 @@
         <v>554.0700000000001</v>
       </c>
     </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="D63" s="6">
+        <v>494.73</v>
+      </c>
+      <c r="E63" s="6">
+        <v>133.8167877197266</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0.3156211376190186</v>
+      </c>
+      <c r="G63" s="6">
+        <v>2</v>
+      </c>
+      <c r="H63" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="I63" s="6">
+        <v>526.0599999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I62"/>
+  <autoFilter ref="A2:I63"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2886,7 +2916,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2901,39 +2931,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2959,17 +2989,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2977,145 +3007,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3123,56 +3153,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="174">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>2026-10-15T06:27:00.786538Z</t>
+  </si>
+  <si>
+    <t>2026-10-15T12:35:42.193561Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1361,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2893,8 +2896,31 @@
         <v>526.0599999999999</v>
       </c>
     </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="6">
+        <v>111.5996475219727</v>
+      </c>
+      <c r="F64" s="6">
+        <v>0.2557317018508911</v>
+      </c>
+      <c r="G64" s="6">
+        <v>2</v>
+      </c>
+      <c r="H64" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="I64" s="6">
+        <v>508.57</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I63"/>
+  <autoFilter ref="A2:I64"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2916,7 +2942,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2931,39 +2957,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2989,17 +3015,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3007,145 +3033,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3153,56 +3179,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="175">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>2026-10-15T12:35:42.193561Z</t>
+  </si>
+  <si>
+    <t>2026-10-15T18:05:03.402279Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1364,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2919,8 +2922,31 @@
         <v>508.57</v>
       </c>
     </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="6">
+        <v>587.669189453125</v>
+      </c>
+      <c r="F65" s="6">
+        <v>2.45569896697998</v>
+      </c>
+      <c r="G65" s="6">
+        <v>2</v>
+      </c>
+      <c r="H65" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="I65" s="6">
+        <v>508.57</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I64"/>
+  <autoFilter ref="A2:I65"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2942,7 +2968,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2957,39 +2983,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3015,17 +3041,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3033,145 +3059,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3179,56 +3205,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="176">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>2026-10-15T18:05:03.402279Z</t>
+  </si>
+  <si>
+    <t>2026-10-15T20:33:31.065428Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1367,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2945,8 +2948,31 @@
         <v>508.57</v>
       </c>
     </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="6">
+        <v>347.2264099121094</v>
+      </c>
+      <c r="F66" s="6">
+        <v>5.332206249237061</v>
+      </c>
+      <c r="G66" s="6">
+        <v>2</v>
+      </c>
+      <c r="H66" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="I66" s="6">
+        <v>508.39</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I65"/>
+  <autoFilter ref="A2:I66"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2968,7 +2994,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2983,39 +3009,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3041,17 +3067,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3059,145 +3085,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3205,56 +3231,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="177">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>2026-10-15T20:33:31.065428Z</t>
+  </si>
+  <si>
+    <t>2026-10-15T23:18:27.022872Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1370,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2971,8 +2974,37 @@
         <v>508.39</v>
       </c>
     </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D67" s="6">
+        <v>452.22</v>
+      </c>
+      <c r="E67" s="6">
+        <v>275.9220581054688</v>
+      </c>
+      <c r="F67" s="6">
+        <v>2.33531665802002</v>
+      </c>
+      <c r="G67" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H67" s="6">
+        <v>-3.46</v>
+      </c>
+      <c r="I67" s="6">
+        <v>489.09</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I66"/>
+  <autoFilter ref="A2:I67"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2994,7 +3026,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3009,39 +3041,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3067,17 +3099,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3085,145 +3117,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3231,56 +3263,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="178">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>2026-10-15T23:18:27.022872Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T01:39:57.253297Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1373,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3003,8 +3006,31 @@
         <v>489.09</v>
       </c>
     </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="6">
+        <v>160.1245574951172</v>
+      </c>
+      <c r="F68" s="6">
+        <v>0.6974166631698608</v>
+      </c>
+      <c r="G68" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H68" s="6">
+        <v>-3.46</v>
+      </c>
+      <c r="I68" s="6">
+        <v>484.95</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I67"/>
+  <autoFilter ref="A2:I68"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3026,7 +3052,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3041,39 +3067,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3099,17 +3125,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3117,145 +3143,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3263,56 +3289,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="179">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>2026-10-16T01:39:57.253297Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T06:22:12.001670Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1376,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3029,8 +3032,31 @@
         <v>484.95</v>
       </c>
     </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="6">
+        <v>191.0065155029297</v>
+      </c>
+      <c r="F69" s="6">
+        <v>0.2574921846389771</v>
+      </c>
+      <c r="G69" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H69" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="I69" s="6">
+        <v>476.8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I68"/>
+  <autoFilter ref="A2:I69"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3052,7 +3078,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3067,39 +3093,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3125,17 +3151,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3143,145 +3169,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3289,56 +3315,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="180">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>2026-10-16T06:22:12.001670Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T12:29:26.193672Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1379,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3055,8 +3058,31 @@
         <v>476.8</v>
       </c>
     </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="6">
+        <v>712.5875854492188</v>
+      </c>
+      <c r="F70" s="6">
+        <v>0.5194904208183289</v>
+      </c>
+      <c r="G70" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H70" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="I70" s="6">
+        <v>476.07</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I69"/>
+  <autoFilter ref="A2:I70"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3078,7 +3104,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3093,39 +3119,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3151,17 +3177,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3169,145 +3195,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3315,56 +3341,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="181">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>2026-10-16T12:29:26.193672Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T17:41:13.773796Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1382,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3081,8 +3084,31 @@
         <v>476.07</v>
       </c>
     </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="6">
+        <v>475.3882751464844</v>
+      </c>
+      <c r="F71" s="6">
+        <v>7.788052082061768</v>
+      </c>
+      <c r="G71" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H71" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="I71" s="6">
+        <v>471.79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I70"/>
+  <autoFilter ref="A2:I71"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3104,7 +3130,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3119,39 +3145,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3177,17 +3203,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3195,145 +3221,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3341,56 +3367,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="182">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>2026-10-16T17:41:13.773796Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T20:05:54.359143Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1385,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3107,8 +3110,31 @@
         <v>471.79</v>
       </c>
     </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="6">
+        <v>403.9035949707031</v>
+      </c>
+      <c r="F72" s="6">
+        <v>9.941727638244629</v>
+      </c>
+      <c r="G72" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H72" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="I72" s="6">
+        <v>470.66</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I71"/>
+  <autoFilter ref="A2:I72"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3130,7 +3156,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3145,39 +3171,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3203,17 +3229,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3221,145 +3247,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3367,56 +3393,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="183">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>2026-10-16T20:05:54.359143Z</t>
+  </si>
+  <si>
+    <t>2026-10-16T23:04:41.274666Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1388,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3133,8 +3136,31 @@
         <v>470.66</v>
       </c>
     </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="6">
+        <v>158.0652923583984</v>
+      </c>
+      <c r="F73" s="6">
+        <v>8.705355644226074</v>
+      </c>
+      <c r="G73" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H73" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="I73" s="6">
+        <v>470.66</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I72"/>
+  <autoFilter ref="A2:I73"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3156,7 +3182,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3171,39 +3197,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3229,17 +3255,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3247,145 +3273,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3393,56 +3419,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="184">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>2026-10-16T23:04:41.274666Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T01:33:07.455050Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1391,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3159,8 +3162,31 @@
         <v>470.66</v>
       </c>
     </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="6">
+        <v>248.1531066894531</v>
+      </c>
+      <c r="F74" s="6">
+        <v>2.297572135925293</v>
+      </c>
+      <c r="G74" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H74" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="I74" s="6">
+        <v>469.04</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I73"/>
+  <autoFilter ref="A2:I74"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3182,7 +3208,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3197,39 +3223,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3255,17 +3281,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3273,145 +3299,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3419,56 +3445,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="185">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>2026-10-17T01:33:07.455050Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T06:10:45.273454Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1394,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3185,8 +3188,35 @@
         <v>469.04</v>
       </c>
     </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="6">
+        <v>4.56</v>
+      </c>
+      <c r="D75" s="6">
+        <v>479.75</v>
+      </c>
+      <c r="E75" s="6">
+        <v>310.5091857910156</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0.4020955562591553</v>
+      </c>
+      <c r="G75" s="6">
+        <v>2</v>
+      </c>
+      <c r="H75" s="6">
+        <v>-2.93</v>
+      </c>
+      <c r="I75" s="6">
+        <v>455.76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I74"/>
+  <autoFilter ref="A2:I75"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3208,7 +3238,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3223,39 +3253,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3281,17 +3311,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3299,145 +3329,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3445,56 +3475,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="186">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>2026-10-17T06:10:45.273454Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T11:49:16.831663Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1397,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3215,8 +3218,31 @@
         <v>455.76</v>
       </c>
     </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="6">
+        <v>479.1106567382812</v>
+      </c>
+      <c r="F76" s="6">
+        <v>0.4124778807163239</v>
+      </c>
+      <c r="G76" s="6">
+        <v>2</v>
+      </c>
+      <c r="H76" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="I76" s="6">
+        <v>451.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I75"/>
+  <autoFilter ref="A2:I76"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3238,7 +3264,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3253,39 +3279,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3311,17 +3337,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3329,145 +3355,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3475,56 +3501,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="187">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>2026-10-17T11:49:16.831663Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T14:25:56.550599Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1400,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3241,8 +3244,31 @@
         <v>451.1</v>
       </c>
     </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="6">
+        <v>504.8936157226562</v>
+      </c>
+      <c r="F77" s="6">
+        <v>0.9117034673690796</v>
+      </c>
+      <c r="G77" s="6">
+        <v>2</v>
+      </c>
+      <c r="H77" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="I77" s="6">
+        <v>447.94</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I76"/>
+  <autoFilter ref="A2:I77"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3264,7 +3290,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3279,39 +3305,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3337,17 +3363,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3355,145 +3381,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3501,56 +3527,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="188">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>2026-10-17T14:25:56.550599Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T17:33:10.408874Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1403,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3267,8 +3270,31 @@
         <v>447.94</v>
       </c>
     </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="6">
+        <v>580.5494995117188</v>
+      </c>
+      <c r="F78" s="6">
+        <v>11.62967681884766</v>
+      </c>
+      <c r="G78" s="6">
+        <v>2</v>
+      </c>
+      <c r="H78" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="I78" s="6">
+        <v>445.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I77"/>
+  <autoFilter ref="A2:I78"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3290,7 +3316,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3305,39 +3331,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3363,17 +3389,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3381,145 +3407,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3527,56 +3553,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="189">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>2026-10-17T17:33:10.408874Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T19:43:49.776268Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1406,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3293,8 +3296,31 @@
         <v>445.83</v>
       </c>
     </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="6">
+        <v>249.3474578857422</v>
+      </c>
+      <c r="F79" s="6">
+        <v>8.300605773925781</v>
+      </c>
+      <c r="G79" s="6">
+        <v>2</v>
+      </c>
+      <c r="H79" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="I79" s="6">
+        <v>442.44</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I78"/>
+  <autoFilter ref="A2:I79"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3316,7 +3342,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3331,39 +3357,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3389,17 +3415,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3407,145 +3433,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3553,56 +3579,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="190">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>2026-10-17T19:43:49.776268Z</t>
+  </si>
+  <si>
+    <t>2026-10-17T21:46:27.774253Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1409,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3319,8 +3322,31 @@
         <v>442.44</v>
       </c>
     </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="6">
+        <v>78.91743469238281</v>
+      </c>
+      <c r="F80" s="6">
+        <v>5.874783515930176</v>
+      </c>
+      <c r="G80" s="6">
+        <v>2</v>
+      </c>
+      <c r="H80" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="I80" s="6">
+        <v>440.55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I79"/>
+  <autoFilter ref="A2:I80"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3342,7 +3368,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3357,39 +3383,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3415,17 +3441,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3433,145 +3459,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3579,56 +3605,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="191">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>2026-10-17T21:46:27.774253Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T00:18:10.799123Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1412,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3345,8 +3348,35 @@
         <v>440.55</v>
       </c>
     </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="6">
+        <v>2.68</v>
+      </c>
+      <c r="D81" s="6">
+        <v>493.04</v>
+      </c>
+      <c r="E81" s="6">
+        <v>201.9989013671875</v>
+      </c>
+      <c r="F81" s="6">
+        <v>6.30055046081543</v>
+      </c>
+      <c r="G81" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H81" s="6">
+        <v>-3.68</v>
+      </c>
+      <c r="I81" s="6">
+        <v>459.12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I80"/>
+  <autoFilter ref="A2:I81"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3368,7 +3398,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3383,39 +3413,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3441,17 +3471,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3459,145 +3489,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3605,56 +3635,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="192">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -399,6 +399,9 @@
   </si>
   <si>
     <t>2026-10-18T00:18:10.799123Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T05:29:55.830599Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1415,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3375,8 +3378,31 @@
         <v>459.12</v>
       </c>
     </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="6">
+        <v>202.6397247314453</v>
+      </c>
+      <c r="F82" s="6">
+        <v>0.6188862919807434</v>
+      </c>
+      <c r="G82" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H82" s="6">
+        <v>-3.68</v>
+      </c>
+      <c r="I82" s="6">
+        <v>451.61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I81"/>
+  <autoFilter ref="A2:I82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3398,7 +3424,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3413,39 +3439,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3471,17 +3497,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3489,145 +3515,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3635,56 +3661,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="193">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>2026-10-18T05:29:55.830599Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T09:53:29.757517Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1418,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3401,8 +3404,31 @@
         <v>451.61</v>
       </c>
     </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="6">
+        <v>221.1932830810547</v>
+      </c>
+      <c r="F83" s="6">
+        <v>0.4933433830738068</v>
+      </c>
+      <c r="G83" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H83" s="6">
+        <v>-3.88</v>
+      </c>
+      <c r="I83" s="6">
+        <v>468.81</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I82"/>
+  <autoFilter ref="A2:I83"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3424,7 +3450,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3439,39 +3465,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3497,17 +3523,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3515,145 +3541,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3661,56 +3687,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="194">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>2026-10-18T09:53:29.757517Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T14:09:55.253028Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1421,7 +1424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3427,8 +3430,31 @@
         <v>468.81</v>
       </c>
     </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="6">
+        <v>359.1458129882812</v>
+      </c>
+      <c r="F84" s="6">
+        <v>1.313726425170898</v>
+      </c>
+      <c r="G84" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H84" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="I84" s="6">
+        <v>464.92</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I83"/>
+  <autoFilter ref="A2:I84"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3450,7 +3476,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3465,39 +3491,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3523,17 +3549,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3541,145 +3567,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3687,56 +3713,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="195">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>2026-10-18T14:09:55.253028Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T17:34:26.962353Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1424,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3453,8 +3456,31 @@
         <v>464.92</v>
       </c>
     </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="6">
+        <v>245.3848571777344</v>
+      </c>
+      <c r="F85" s="6">
+        <v>2.766201496124268</v>
+      </c>
+      <c r="G85" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H85" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="I85" s="6">
+        <v>463.28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I84"/>
+  <autoFilter ref="A2:I85"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3476,7 +3502,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3491,39 +3517,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3549,17 +3575,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3567,145 +3593,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3713,56 +3739,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="196">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>2026-10-18T17:34:26.962353Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T19:41:17.448558Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1427,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3479,8 +3482,31 @@
         <v>463.28</v>
       </c>
     </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="6">
+        <v>224.7544860839844</v>
+      </c>
+      <c r="F86" s="6">
+        <v>4.0725417137146</v>
+      </c>
+      <c r="G86" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H86" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="I86" s="6">
+        <v>455.05</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I85"/>
+  <autoFilter ref="A2:I86"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3502,7 +3528,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3517,39 +3543,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3575,17 +3601,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3593,145 +3619,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3739,56 +3765,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="197">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>2026-10-18T19:41:17.448558Z</t>
+  </si>
+  <si>
+    <t>2026-10-18T21:54:01.571207Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1430,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3505,8 +3508,35 @@
         <v>455.05</v>
       </c>
     </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="6">
+        <v>3.56</v>
+      </c>
+      <c r="D87" s="6">
+        <v>422.57</v>
+      </c>
+      <c r="E87" s="6">
+        <v>241.3448181152344</v>
+      </c>
+      <c r="F87" s="6">
+        <v>3.614439249038696</v>
+      </c>
+      <c r="G87" s="6">
+        <v>2</v>
+      </c>
+      <c r="H87" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="I87" s="6">
+        <v>424.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I86"/>
+  <autoFilter ref="A2:I87"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3528,7 +3558,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3543,39 +3573,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3601,17 +3631,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3619,145 +3649,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3765,56 +3795,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="198">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>2026-10-18T21:54:01.571207Z</t>
+  </si>
+  <si>
+    <t>2026-10-19T00:29:39.586995Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1433,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3535,8 +3538,31 @@
         <v>424.87</v>
       </c>
     </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="6">
+        <v>208.214599609375</v>
+      </c>
+      <c r="F88" s="6">
+        <v>2.158342123031616</v>
+      </c>
+      <c r="G88" s="6">
+        <v>2</v>
+      </c>
+      <c r="H88" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="I88" s="6">
+        <v>423.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I87"/>
+  <autoFilter ref="A2:I88"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3558,7 +3584,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3573,39 +3599,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3631,17 +3657,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3649,145 +3675,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3795,56 +3821,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="199">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>2026-10-19T00:29:39.586995Z</t>
+  </si>
+  <si>
+    <t>2026-10-19T05:47:14.835565Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1436,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3561,8 +3564,31 @@
         <v>423.02</v>
       </c>
     </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="6">
+        <v>215.4522857666016</v>
+      </c>
+      <c r="F89" s="6">
+        <v>0.6789541840553284</v>
+      </c>
+      <c r="G89" s="6">
+        <v>2</v>
+      </c>
+      <c r="H89" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="I89" s="6">
+        <v>423.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I88"/>
+  <autoFilter ref="A2:I89"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3584,7 +3610,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3599,39 +3625,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3657,17 +3683,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3675,145 +3701,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3821,56 +3847,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="200">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>2026-10-19T05:47:14.835565Z</t>
+  </si>
+  <si>
+    <t>2026-10-19T11:15:59.267590Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1439,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3587,8 +3590,31 @@
         <v>423.02</v>
       </c>
     </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="6">
+        <v>271.6630859375</v>
+      </c>
+      <c r="F90" s="6">
+        <v>0.7749086022377014</v>
+      </c>
+      <c r="G90" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H90" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="I90" s="6">
+        <v>388.9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I89"/>
+  <autoFilter ref="A2:I90"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3610,7 +3636,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3625,39 +3651,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3683,17 +3709,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3701,145 +3727,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3847,56 +3873,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="201">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>2026-10-19T11:15:59.267590Z</t>
+  </si>
+  <si>
+    <t>2026-10-19T17:47:48.327069Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1442,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3613,8 +3616,31 @@
         <v>388.9</v>
       </c>
     </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="6">
+        <v>449.6478271484375</v>
+      </c>
+      <c r="F91" s="6">
+        <v>4.275919914245605</v>
+      </c>
+      <c r="G91" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H91" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="I91" s="6">
+        <v>376.33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I90"/>
+  <autoFilter ref="A2:I91"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3636,7 +3662,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3651,39 +3677,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3709,17 +3735,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3727,145 +3753,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3873,56 +3899,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="202">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>2026-10-19T17:47:48.327069Z</t>
+  </si>
+  <si>
+    <t>2026-10-19T22:39:49.070759Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1445,7 +1448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3639,8 +3642,31 @@
         <v>376.33</v>
       </c>
     </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="6">
+        <v>230.5890197753906</v>
+      </c>
+      <c r="F92" s="6">
+        <v>9.083964347839355</v>
+      </c>
+      <c r="G92" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H92" s="6">
+        <v>-3.56</v>
+      </c>
+      <c r="I92" s="6">
+        <v>392.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I91"/>
+  <autoFilter ref="A2:I92"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3662,7 +3688,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3677,39 +3703,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3735,17 +3761,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3753,145 +3779,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3899,56 +3925,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="203">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t>2026-10-19T22:39:49.070759Z</t>
+  </si>
+  <si>
+    <t>2026-10-20T01:16:52.932927Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1448,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3665,8 +3668,37 @@
         <v>392.2</v>
       </c>
     </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B93" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="C93" s="6">
+        <v>-0.76</v>
+      </c>
+      <c r="D93" s="6">
+        <v>353.26</v>
+      </c>
+      <c r="E93" s="6">
+        <v>239.6266326904297</v>
+      </c>
+      <c r="F93" s="6">
+        <v>3.966278076171875</v>
+      </c>
+      <c r="G93" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H93" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="I93" s="6">
+        <v>387.25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I92"/>
+  <autoFilter ref="A2:I93"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3688,7 +3720,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3703,39 +3735,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3761,17 +3793,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3779,145 +3811,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3925,56 +3957,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="204">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t>2026-10-20T01:16:52.932927Z</t>
+  </si>
+  <si>
+    <t>2026-10-20T06:35:49.563610Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1451,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3697,8 +3700,31 @@
         <v>387.25</v>
       </c>
     </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="6">
+        <v>116.0773468017578</v>
+      </c>
+      <c r="F94" s="6">
+        <v>0.2656556665897369</v>
+      </c>
+      <c r="G94" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H94" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="I94" s="6">
+        <v>387.25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I93"/>
+  <autoFilter ref="A2:I94"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3720,7 +3746,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3735,39 +3761,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3793,17 +3819,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3811,145 +3837,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3957,56 +3983,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="205">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -438,6 +438,9 @@
   </si>
   <si>
     <t>2026-10-20T06:35:49.563610Z</t>
+  </si>
+  <si>
+    <t>2026-10-20T12:10:43.963127Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1454,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3723,8 +3726,31 @@
         <v>387.25</v>
       </c>
     </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="6">
+        <v>456.238525390625</v>
+      </c>
+      <c r="F95" s="6">
+        <v>0.9142044186592102</v>
+      </c>
+      <c r="G95" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H95" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="I95" s="6">
+        <v>389.73</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I94"/>
+  <autoFilter ref="A2:I95"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3746,7 +3772,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3761,39 +3787,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3819,17 +3845,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3837,145 +3863,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3983,56 +4009,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="206">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>2026-10-20T12:10:43.963127Z</t>
+  </si>
+  <si>
+    <t>2026-10-20T17:32:20.860187Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1457,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3749,8 +3752,31 @@
         <v>389.73</v>
       </c>
     </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="6">
+        <v>260.4497985839844</v>
+      </c>
+      <c r="F96" s="6">
+        <v>6.877877712249756</v>
+      </c>
+      <c r="G96" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H96" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="I96" s="6">
+        <v>398.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I95"/>
+  <autoFilter ref="A2:I96"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3772,7 +3798,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3787,39 +3813,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3845,17 +3871,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3863,145 +3889,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4009,56 +4035,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="207">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>2026-10-20T17:32:20.860187Z</t>
+  </si>
+  <si>
+    <t>2026-10-20T20:53:52.908956Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1460,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3775,8 +3778,31 @@
         <v>398.02</v>
       </c>
     </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="6">
+        <v>200.3239898681641</v>
+      </c>
+      <c r="F97" s="6">
+        <v>10.2202262878418</v>
+      </c>
+      <c r="G97" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H97" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="I97" s="6">
+        <v>398.33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I96"/>
+  <autoFilter ref="A2:I97"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3798,7 +3824,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3813,39 +3839,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3871,17 +3897,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3889,145 +3915,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4035,56 +4061,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="208">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>2026-10-20T20:53:52.908956Z</t>
+  </si>
+  <si>
+    <t>2026-10-21T00:52:07.507619Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1463,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3801,8 +3804,31 @@
         <v>398.33</v>
       </c>
     </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="6">
+        <v>291.7948608398438</v>
+      </c>
+      <c r="F98" s="6">
+        <v>2.192428112030029</v>
+      </c>
+      <c r="G98" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H98" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="I98" s="6">
+        <v>400.42</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I97"/>
+  <autoFilter ref="A2:I98"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3824,7 +3850,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3839,39 +3865,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3897,17 +3923,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3915,145 +3941,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4061,56 +4087,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="209">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>2026-10-21T00:52:07.507619Z</t>
+  </si>
+  <si>
+    <t>2026-10-21T05:52:15.807915Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1466,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3827,8 +3830,31 @@
         <v>400.42</v>
       </c>
     </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="6">
+        <v>28.94950866699219</v>
+      </c>
+      <c r="F99" s="6">
+        <v>0.9114839434623718</v>
+      </c>
+      <c r="G99" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="H99" s="6">
+        <v>-6.98</v>
+      </c>
+      <c r="I99" s="6">
+        <v>482.91</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I98"/>
+  <autoFilter ref="A2:I99"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3850,7 +3876,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3865,39 +3891,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3923,17 +3949,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3941,145 +3967,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4087,56 +4113,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="210">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -453,6 +453,9 @@
   </si>
   <si>
     <t>2026-10-21T05:52:15.807915Z</t>
+  </si>
+  <si>
+    <t>2026-10-21T10:36:30.926434Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1469,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3853,8 +3856,31 @@
         <v>482.91</v>
       </c>
     </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="6">
+        <v>99.99652099609375</v>
+      </c>
+      <c r="F100" s="6">
+        <v>0.3227868676185608</v>
+      </c>
+      <c r="G100" s="6">
+        <v>4</v>
+      </c>
+      <c r="H100" s="6">
+        <v>-8.32</v>
+      </c>
+      <c r="I100" s="6">
+        <v>476.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I99"/>
+  <autoFilter ref="A2:I100"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3876,7 +3902,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3891,39 +3917,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3949,17 +3975,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3967,145 +3993,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4113,56 +4139,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="211">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -456,6 +456,9 @@
   </si>
   <si>
     <t>2026-10-21T10:36:30.926434Z</t>
+  </si>
+  <si>
+    <t>2026-10-21T15:37:35.463803Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1472,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3879,8 +3882,31 @@
         <v>476.1</v>
       </c>
     </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="6">
+        <v>151.6186981201172</v>
+      </c>
+      <c r="F101" s="6">
+        <v>0.5227814912796021</v>
+      </c>
+      <c r="G101" s="6">
+        <v>4</v>
+      </c>
+      <c r="H101" s="6">
+        <v>-8.32</v>
+      </c>
+      <c r="I101" s="6">
+        <v>476.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I100"/>
+  <autoFilter ref="A2:I101"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3902,7 +3928,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3917,39 +3943,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3975,17 +4001,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3993,145 +4019,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4139,56 +4165,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="212">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t>2026-10-21T15:37:35.463803Z</t>
+  </si>
+  <si>
+    <t>2026-10-21T19:37:10.610359Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1475,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3905,8 +3908,31 @@
         <v>476.1</v>
       </c>
     </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="6">
+        <v>156.19775390625</v>
+      </c>
+      <c r="F102" s="6">
+        <v>6.36051082611084</v>
+      </c>
+      <c r="G102" s="6">
+        <v>4</v>
+      </c>
+      <c r="H102" s="6">
+        <v>-6.89</v>
+      </c>
+      <c r="I102" s="6">
+        <v>476.1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I101"/>
+  <autoFilter ref="A2:I102"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3928,7 +3954,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3943,39 +3969,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4001,17 +4027,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4019,145 +4045,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4165,56 +4191,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="213">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>2026-10-21T19:37:10.610359Z</t>
+  </si>
+  <si>
+    <t>2026-10-21T22:44:32.735139Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1478,7 +1481,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3931,8 +3934,37 @@
         <v>476.1</v>
       </c>
     </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B103" s="6">
+        <v>3.67</v>
+      </c>
+      <c r="C103" s="6">
+        <v>-2.57</v>
+      </c>
+      <c r="D103" s="6">
+        <v>453.1</v>
+      </c>
+      <c r="E103" s="6">
+        <v>314.5800170898438</v>
+      </c>
+      <c r="F103" s="6">
+        <v>10.79413986206055</v>
+      </c>
+      <c r="G103" s="6">
+        <v>4</v>
+      </c>
+      <c r="H103" s="6">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="I103" s="6">
+        <v>514.59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I102"/>
+  <autoFilter ref="A2:I103"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3954,7 +3986,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3969,39 +4001,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4027,17 +4059,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4045,145 +4077,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4191,56 +4223,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="214">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -465,6 +465,9 @@
   </si>
   <si>
     <t>2026-10-21T22:44:32.735139Z</t>
+  </si>
+  <si>
+    <t>2026-10-22T01:51:52.022680Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1481,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3963,8 +3966,31 @@
         <v>514.59</v>
       </c>
     </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="6">
+        <v>239.4844207763672</v>
+      </c>
+      <c r="F104" s="6">
+        <v>1.980938315391541</v>
+      </c>
+      <c r="G104" s="6">
+        <v>4</v>
+      </c>
+      <c r="H104" s="6">
+        <v>-7.13</v>
+      </c>
+      <c r="I104" s="6">
+        <v>514.59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I103"/>
+  <autoFilter ref="A2:I104"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3986,7 +4012,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4001,39 +4027,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4059,17 +4085,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4077,145 +4103,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4223,56 +4249,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="215">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -468,6 +468,9 @@
   </si>
   <si>
     <t>2026-10-22T01:51:52.022680Z</t>
+  </si>
+  <si>
+    <t>2026-10-22T07:57:50.274023Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1484,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3989,8 +3992,31 @@
         <v>514.59</v>
       </c>
     </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="6">
+        <v>248.0570220947266</v>
+      </c>
+      <c r="F105" s="6">
+        <v>0.3182720839977264</v>
+      </c>
+      <c r="G105" s="6">
+        <v>4</v>
+      </c>
+      <c r="H105" s="6">
+        <v>-7</v>
+      </c>
+      <c r="I105" s="6">
+        <v>514.59</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I104"/>
+  <autoFilter ref="A2:I105"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4012,7 +4038,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4027,39 +4053,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4085,17 +4111,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4103,145 +4129,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4249,56 +4275,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="216">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>2026-10-22T07:57:50.274023Z</t>
+  </si>
+  <si>
+    <t>2026-10-22T14:06:27.708515Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1487,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4015,8 +4018,33 @@
         <v>514.59</v>
       </c>
     </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B106" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="6">
+        <v>270.4253540039062</v>
+      </c>
+      <c r="F106" s="6">
+        <v>0.6494896411895752</v>
+      </c>
+      <c r="G106" s="6">
+        <v>4.67</v>
+      </c>
+      <c r="H106" s="6">
+        <v>-8.93</v>
+      </c>
+      <c r="I106" s="6">
+        <v>488.19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I105"/>
+  <autoFilter ref="A2:I106"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4038,7 +4066,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4053,39 +4081,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4111,17 +4139,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4129,145 +4157,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4275,56 +4303,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="217">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -474,6 +474,9 @@
   </si>
   <si>
     <t>2026-10-22T14:06:27.708515Z</t>
+  </si>
+  <si>
+    <t>2026-10-22T18:48:53.248923Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1490,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4043,8 +4046,31 @@
         <v>488.19</v>
       </c>
     </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="6">
+        <v>639.2919921875</v>
+      </c>
+      <c r="F107" s="6">
+        <v>4.260687828063965</v>
+      </c>
+      <c r="G107" s="6">
+        <v>4.67</v>
+      </c>
+      <c r="H107" s="6">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="I107" s="6">
+        <v>482.84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I106"/>
+  <autoFilter ref="A2:I107"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4066,7 +4092,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4081,39 +4107,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4139,17 +4165,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4157,145 +4183,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4303,56 +4329,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="218">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -477,6 +477,9 @@
   </si>
   <si>
     <t>2026-10-22T18:48:53.248923Z</t>
+  </si>
+  <si>
+    <t>2026-10-22T22:45:47.571298Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1493,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4069,8 +4072,31 @@
         <v>482.84</v>
       </c>
     </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="6">
+        <v>268.712646484375</v>
+      </c>
+      <c r="F108" s="6">
+        <v>5.929080009460449</v>
+      </c>
+      <c r="G108" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="H108" s="6">
+        <v>-7.71</v>
+      </c>
+      <c r="I108" s="6">
+        <v>476.65</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I107"/>
+  <autoFilter ref="A2:I108"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4092,7 +4118,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4107,39 +4133,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4165,17 +4191,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4183,145 +4209,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4329,56 +4355,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="219">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t>2026-10-22T22:45:47.571298Z</t>
+  </si>
+  <si>
+    <t>2026-10-23T01:57:55.197180Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1496,7 +1499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4095,8 +4098,31 @@
         <v>476.65</v>
       </c>
     </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="6">
+        <v>185.8605041503906</v>
+      </c>
+      <c r="F109" s="6">
+        <v>1.272260785102844</v>
+      </c>
+      <c r="G109" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="H109" s="6">
+        <v>-7.71</v>
+      </c>
+      <c r="I109" s="6">
+        <v>473.64</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I108"/>
+  <autoFilter ref="A2:I109"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4118,7 +4144,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4133,39 +4159,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4191,17 +4217,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4209,145 +4235,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4355,56 +4381,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="220">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -483,6 +483,9 @@
   </si>
   <si>
     <t>2026-10-23T01:57:55.197180Z</t>
+  </si>
+  <si>
+    <t>2026-10-23T07:59:32.003405Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1499,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4121,8 +4124,31 @@
         <v>473.64</v>
       </c>
     </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="6">
+        <v>417.6680297851562</v>
+      </c>
+      <c r="F110" s="6">
+        <v>0.3133898377418518</v>
+      </c>
+      <c r="G110" s="6">
+        <v>4</v>
+      </c>
+      <c r="H110" s="6">
+        <v>-7.23</v>
+      </c>
+      <c r="I110" s="6">
+        <v>464.61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I109"/>
+  <autoFilter ref="A2:I110"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4144,7 +4170,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4159,39 +4185,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4217,17 +4243,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4235,145 +4261,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4381,56 +4407,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="221">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -486,6 +486,9 @@
   </si>
   <si>
     <t>2026-10-23T07:59:32.003405Z</t>
+  </si>
+  <si>
+    <t>2026-10-23T13:49:05.621206Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1502,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I110"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4147,8 +4150,31 @@
         <v>464.61</v>
       </c>
     </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="6">
+        <v>2309.087646484375</v>
+      </c>
+      <c r="F111" s="6">
+        <v>0.5681942701339722</v>
+      </c>
+      <c r="G111" s="6">
+        <v>2</v>
+      </c>
+      <c r="H111" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I111" s="6">
+        <v>465.71</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I110"/>
+  <autoFilter ref="A2:I111"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4170,7 +4196,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4185,39 +4211,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4243,17 +4269,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4261,145 +4287,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4407,56 +4433,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="222">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -489,6 +489,9 @@
   </si>
   <si>
     <t>2026-10-23T13:49:05.621206Z</t>
+  </si>
+  <si>
+    <t>2026-10-23T18:43:08.588921Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1505,7 +1508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4173,8 +4176,31 @@
         <v>465.71</v>
       </c>
     </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="6">
+        <v>2489.510986328125</v>
+      </c>
+      <c r="F112" s="6">
+        <v>3.789721965789795</v>
+      </c>
+      <c r="G112" s="6">
+        <v>2</v>
+      </c>
+      <c r="H112" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I112" s="6">
+        <v>459.38</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I111"/>
+  <autoFilter ref="A2:I112"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4196,7 +4222,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4211,39 +4237,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4269,17 +4295,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4287,145 +4313,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4433,56 +4459,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="223">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>2026-10-23T18:43:08.588921Z</t>
+  </si>
+  <si>
+    <t>2026-10-23T22:26:22.576983Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1508,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4199,8 +4202,31 @@
         <v>459.38</v>
       </c>
     </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="6">
+        <v>927.7470703125</v>
+      </c>
+      <c r="F113" s="6">
+        <v>3.085972547531128</v>
+      </c>
+      <c r="G113" s="6">
+        <v>2</v>
+      </c>
+      <c r="H113" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I113" s="6">
+        <v>454.25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I112"/>
+  <autoFilter ref="A2:I113"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4222,7 +4248,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4237,39 +4263,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4295,17 +4321,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4313,145 +4339,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4459,56 +4485,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="224">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -495,6 +495,9 @@
   </si>
   <si>
     <t>2026-10-23T22:26:22.576983Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T00:04:40.272221Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1511,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4225,8 +4228,31 @@
         <v>454.25</v>
       </c>
     </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="6">
+        <v>555.5672607421875</v>
+      </c>
+      <c r="F114" s="6">
+        <v>0.9177561402320862</v>
+      </c>
+      <c r="G114" s="6">
+        <v>2</v>
+      </c>
+      <c r="H114" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I114" s="6">
+        <v>453.91</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I113"/>
+  <autoFilter ref="A2:I114"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4248,7 +4274,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4263,39 +4289,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4321,17 +4347,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4339,145 +4365,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4485,56 +4511,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="225">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -498,6 +498,9 @@
   </si>
   <si>
     <t>2026-10-24T00:04:40.272221Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T05:41:38.815380Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1514,7 +1517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4251,8 +4254,31 @@
         <v>453.91</v>
       </c>
     </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="6">
+        <v>817.6160888671875</v>
+      </c>
+      <c r="F115" s="6">
+        <v>0.2429192215204239</v>
+      </c>
+      <c r="G115" s="6">
+        <v>2</v>
+      </c>
+      <c r="H115" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I115" s="6">
+        <v>445.99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I114"/>
+  <autoFilter ref="A2:I115"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4274,7 +4300,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4289,39 +4315,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4347,17 +4373,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4365,145 +4391,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4511,56 +4537,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="226">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>2026-10-24T05:41:38.815380Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T09:48:22.933443Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1517,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4277,8 +4280,31 @@
         <v>445.99</v>
       </c>
     </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="6">
+        <v>963.4166870117188</v>
+      </c>
+      <c r="F116" s="6">
+        <v>0.2998511493206024</v>
+      </c>
+      <c r="G116" s="6">
+        <v>2</v>
+      </c>
+      <c r="H116" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I116" s="6">
+        <v>439.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I115"/>
+  <autoFilter ref="A2:I116"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4300,7 +4326,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4315,39 +4341,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4373,17 +4399,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4391,145 +4417,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4537,56 +4563,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="227">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -504,6 +504,9 @@
   </si>
   <si>
     <t>2026-10-24T09:48:22.933443Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T14:07:57.255976Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1520,7 +1523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4303,8 +4306,31 @@
         <v>439.5</v>
       </c>
     </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="6">
+        <v>2141.980224609375</v>
+      </c>
+      <c r="F117" s="6">
+        <v>0.3250046670436859</v>
+      </c>
+      <c r="G117" s="6">
+        <v>2</v>
+      </c>
+      <c r="H117" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="I117" s="6">
+        <v>424.28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I116"/>
+  <autoFilter ref="A2:I117"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4326,7 +4352,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4341,39 +4367,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4399,17 +4425,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4417,145 +4443,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4563,56 +4589,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="228">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -507,6 +507,9 @@
   </si>
   <si>
     <t>2026-10-24T14:07:57.255976Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T17:36:31.198525Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1523,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4329,8 +4332,37 @@
         <v>424.28</v>
       </c>
     </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B118" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="C118" s="6">
+        <v>-0.24</v>
+      </c>
+      <c r="D118" s="6">
+        <v>415.98</v>
+      </c>
+      <c r="E118" s="6">
+        <v>2769.367919921875</v>
+      </c>
+      <c r="F118" s="6">
+        <v>1.349954843521118</v>
+      </c>
+      <c r="G118" s="6">
+        <v>2</v>
+      </c>
+      <c r="H118" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="I118" s="6">
+        <v>419.65</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I117"/>
+  <autoFilter ref="A2:I118"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4352,7 +4384,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4367,39 +4399,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4425,17 +4457,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4443,145 +4475,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4589,56 +4621,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="229">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -510,6 +510,9 @@
   </si>
   <si>
     <t>2026-10-24T17:36:31.198525Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:47:50.595806Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1526,7 +1529,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4361,8 +4364,31 @@
         <v>419.65</v>
       </c>
     </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="6">
+        <v>1793.492797851562</v>
+      </c>
+      <c r="F119" s="6">
+        <v>3.163056373596191</v>
+      </c>
+      <c r="G119" s="6">
+        <v>2</v>
+      </c>
+      <c r="H119" s="6">
+        <v>-4.73</v>
+      </c>
+      <c r="I119" s="6">
+        <v>419.65</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I118"/>
+  <autoFilter ref="A2:I119"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4384,7 +4410,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4399,39 +4425,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4457,17 +4483,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4475,145 +4501,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4621,56 +4647,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="230">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -513,6 +513,9 @@
   </si>
   <si>
     <t>2026-10-24T19:47:50.595806Z</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:44:31.205718Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1529,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4387,8 +4390,31 @@
         <v>419.65</v>
       </c>
     </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="6">
+        <v>1036.955444335938</v>
+      </c>
+      <c r="F120" s="6">
+        <v>4.166478633880615</v>
+      </c>
+      <c r="G120" s="6">
+        <v>2</v>
+      </c>
+      <c r="H120" s="6">
+        <v>-4.73</v>
+      </c>
+      <c r="I120" s="6">
+        <v>419.65</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I119"/>
+  <autoFilter ref="A2:I120"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4410,7 +4436,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4425,39 +4451,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4483,17 +4509,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4501,145 +4527,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4647,56 +4673,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="231">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>2026-10-24T22:44:31.205718Z</t>
+  </si>
+  <si>
+    <t>2026-10-25T01:38:36.876999Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1532,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4413,8 +4416,31 @@
         <v>419.65</v>
       </c>
     </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B121" s="4"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="6">
+        <v>838.4881591796875</v>
+      </c>
+      <c r="F121" s="6">
+        <v>1.342891454696655</v>
+      </c>
+      <c r="G121" s="6">
+        <v>2</v>
+      </c>
+      <c r="H121" s="6">
+        <v>-4.73</v>
+      </c>
+      <c r="I121" s="6">
+        <v>419.65</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I120"/>
+  <autoFilter ref="A2:I121"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4436,7 +4462,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4451,39 +4477,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4509,17 +4535,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4527,145 +4553,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4673,56 +4699,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="232">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>2026-10-25T01:38:36.876999Z</t>
+  </si>
+  <si>
+    <t>2026-10-25T06:51:19.412625Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1535,7 +1538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4439,8 +4442,31 @@
         <v>419.65</v>
       </c>
     </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B122" s="4"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="6">
+        <v>486.5783081054688</v>
+      </c>
+      <c r="F122" s="6">
+        <v>0.4231331944465637</v>
+      </c>
+      <c r="G122" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H122" s="6">
+        <v>-4.26</v>
+      </c>
+      <c r="I122" s="6">
+        <v>411.96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I121"/>
+  <autoFilter ref="A2:I122"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4462,7 +4488,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4477,39 +4503,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4535,17 +4561,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4553,145 +4579,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4699,56 +4725,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$123</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="233">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>2026-10-25T06:51:19.412625Z</t>
+  </si>
+  <si>
+    <t>2026-10-25T12:47:15.994280Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1538,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4465,8 +4468,35 @@
         <v>411.96</v>
       </c>
     </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B123" s="4"/>
+      <c r="C123" s="6">
+        <v>-3.81</v>
+      </c>
+      <c r="D123" s="6">
+        <v>353.9</v>
+      </c>
+      <c r="E123" s="6">
+        <v>1749.71533203125</v>
+      </c>
+      <c r="F123" s="6">
+        <v>0.3700136244297028</v>
+      </c>
+      <c r="G123" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H123" s="6">
+        <v>-4.24</v>
+      </c>
+      <c r="I123" s="6">
+        <v>410.35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I122"/>
+  <autoFilter ref="A2:I123"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4488,7 +4518,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4503,39 +4533,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4561,17 +4591,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4579,145 +4609,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4725,56 +4755,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="234">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -525,6 +525,9 @@
   </si>
   <si>
     <t>2026-10-25T12:47:15.994280Z</t>
+  </si>
+  <si>
+    <t>2026-10-25T17:26:58.634962Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1541,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4495,8 +4498,31 @@
         <v>410.35</v>
       </c>
     </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B124" s="4"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="6">
+        <v>2286.977783203125</v>
+      </c>
+      <c r="F124" s="6">
+        <v>2.322928190231323</v>
+      </c>
+      <c r="G124" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H124" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="I124" s="6">
+        <v>410.35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I123"/>
+  <autoFilter ref="A2:I124"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4518,7 +4544,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4533,39 +4559,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4591,17 +4617,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4609,145 +4635,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4755,56 +4781,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="235">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -528,6 +528,9 @@
   </si>
   <si>
     <t>2026-10-25T17:26:58.634962Z</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:58:02.366597Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1544,7 +1547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4521,8 +4524,31 @@
         <v>410.35</v>
       </c>
     </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B125" s="4"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="6">
+        <v>2328.18896484375</v>
+      </c>
+      <c r="F125" s="6">
+        <v>8.16737174987793</v>
+      </c>
+      <c r="G125" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H125" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="I125" s="6">
+        <v>410.35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I124"/>
+  <autoFilter ref="A2:I125"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4544,7 +4570,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4559,39 +4585,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4617,17 +4643,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4635,145 +4661,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4781,56 +4807,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="236">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -531,6 +531,9 @@
   </si>
   <si>
     <t>2026-10-25T19:58:02.366597Z</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:51:59.363904Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1547,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4547,8 +4550,31 @@
         <v>410.35</v>
       </c>
     </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B126" s="4"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="6">
+        <v>1447.53369140625</v>
+      </c>
+      <c r="F126" s="6">
+        <v>9.246943473815918</v>
+      </c>
+      <c r="G126" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H126" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="I126" s="6">
+        <v>410.35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I125"/>
+  <autoFilter ref="A2:I126"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4570,7 +4596,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4585,39 +4611,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4643,17 +4669,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4661,145 +4687,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4807,56 +4833,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="237">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -534,6 +534,9 @@
   </si>
   <si>
     <t>2026-10-25T22:51:59.363904Z</t>
+  </si>
+  <si>
+    <t>2026-10-26T01:42:30.124014Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1550,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4573,8 +4576,31 @@
         <v>410.35</v>
       </c>
     </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B127" s="4"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="6">
+        <v>1184.121826171875</v>
+      </c>
+      <c r="F127" s="6">
+        <v>1.289700031280518</v>
+      </c>
+      <c r="G127" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H127" s="6">
+        <v>-3.53</v>
+      </c>
+      <c r="I127" s="6">
+        <v>405.58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I126"/>
+  <autoFilter ref="A2:I127"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4596,7 +4622,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4611,39 +4637,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4669,17 +4695,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4687,145 +4713,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4833,56 +4859,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="238">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -537,6 +537,9 @@
   </si>
   <si>
     <t>2026-10-26T01:42:30.124014Z</t>
+  </si>
+  <si>
+    <t>2026-10-26T07:00:25.656217Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1553,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4599,8 +4602,31 @@
         <v>405.58</v>
       </c>
     </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B128" s="4"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="6">
+        <v>1354.910278320312</v>
+      </c>
+      <c r="F128" s="6">
+        <v>0.3424632847309113</v>
+      </c>
+      <c r="G128" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H128" s="6">
+        <v>-3.45</v>
+      </c>
+      <c r="I128" s="6">
+        <v>405.62</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I127"/>
+  <autoFilter ref="A2:I128"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4622,7 +4648,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4637,39 +4663,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4695,17 +4721,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4713,145 +4739,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4859,56 +4885,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="239">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t>2026-10-26T07:00:25.656217Z</t>
+  </si>
+  <si>
+    <t>2026-10-26T14:34:53.035129Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1556,7 +1559,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I128"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4625,8 +4628,31 @@
         <v>405.62</v>
       </c>
     </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B129" s="4"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="6">
+        <v>2033.809204101562</v>
+      </c>
+      <c r="F129" s="6">
+        <v>1.303479075431824</v>
+      </c>
+      <c r="G129" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H129" s="6">
+        <v>-3.44</v>
+      </c>
+      <c r="I129" s="6">
+        <v>405.62</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I128"/>
+  <autoFilter ref="A2:I129"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4648,7 +4674,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4663,39 +4689,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4721,17 +4747,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4739,145 +4765,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4885,56 +4911,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="240">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -543,6 +543,9 @@
   </si>
   <si>
     <t>2026-10-26T14:34:53.035129Z</t>
+  </si>
+  <si>
+    <t>2026-10-26T20:09:33.639910Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1559,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4651,8 +4654,31 @@
         <v>405.62</v>
       </c>
     </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B130" s="4"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="6">
+        <v>911.0018310546875</v>
+      </c>
+      <c r="F130" s="6">
+        <v>13.10039901733398</v>
+      </c>
+      <c r="G130" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H130" s="6">
+        <v>-3.44</v>
+      </c>
+      <c r="I130" s="6">
+        <v>405.62</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I129"/>
+  <autoFilter ref="A2:I130"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4674,7 +4700,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4689,39 +4715,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4747,17 +4773,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4765,145 +4791,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4911,56 +4937,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="241">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -546,6 +546,9 @@
   </si>
   <si>
     <t>2026-10-26T20:09:33.639910Z</t>
+  </si>
+  <si>
+    <t>2026-10-27T00:05:50.785890Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1562,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4677,8 +4680,31 @@
         <v>405.62</v>
       </c>
     </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B131" s="4"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="6">
+        <v>365.4983825683594</v>
+      </c>
+      <c r="F131" s="6">
+        <v>5.044337749481201</v>
+      </c>
+      <c r="G131" s="6">
+        <v>2</v>
+      </c>
+      <c r="H131" s="6">
+        <v>-4.42</v>
+      </c>
+      <c r="I131" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I130"/>
+  <autoFilter ref="A2:I131"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4700,7 +4726,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4715,39 +4741,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4773,17 +4799,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4791,145 +4817,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4937,56 +4963,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="242">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -549,6 +549,9 @@
   </si>
   <si>
     <t>2026-10-27T00:05:50.785890Z</t>
+  </si>
+  <si>
+    <t>2026-10-27T05:36:10.320851Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1565,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4703,8 +4706,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B132" s="4"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="6">
+        <v>201.2698364257812</v>
+      </c>
+      <c r="F132" s="6">
+        <v>0.6403393745422363</v>
+      </c>
+      <c r="G132" s="6">
+        <v>2</v>
+      </c>
+      <c r="H132" s="6">
+        <v>-4.81</v>
+      </c>
+      <c r="I132" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I131"/>
+  <autoFilter ref="A2:I132"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4726,7 +4752,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4741,39 +4767,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4799,17 +4825,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4817,145 +4843,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4963,56 +4989,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="243">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -552,6 +552,9 @@
   </si>
   <si>
     <t>2026-10-27T05:36:10.320851Z</t>
+  </si>
+  <si>
+    <t>2026-10-27T10:59:07.961449Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1568,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4729,8 +4732,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B133" s="4"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="6">
+        <v>644.9476318359375</v>
+      </c>
+      <c r="F133" s="6">
+        <v>0.647748589515686</v>
+      </c>
+      <c r="G133" s="6">
+        <v>2</v>
+      </c>
+      <c r="H133" s="6">
+        <v>-4.81</v>
+      </c>
+      <c r="I133" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I132"/>
+  <autoFilter ref="A2:I133"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4752,7 +4778,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4767,39 +4793,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4825,17 +4851,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4843,145 +4869,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4989,56 +5015,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="244">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -555,6 +555,9 @@
   </si>
   <si>
     <t>2026-10-27T10:59:07.961449Z</t>
+  </si>
+  <si>
+    <t>2026-10-27T16:53:50.152964Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1571,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4755,8 +4758,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B134" s="4"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="6">
+        <v>1545.7685546875</v>
+      </c>
+      <c r="F134" s="6">
+        <v>2.217857122421265</v>
+      </c>
+      <c r="G134" s="6">
+        <v>2</v>
+      </c>
+      <c r="H134" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="I134" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I133"/>
+  <autoFilter ref="A2:I134"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4778,7 +4804,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4793,39 +4819,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4851,17 +4877,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4869,145 +4895,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5015,56 +5041,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="245">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -558,6 +558,9 @@
   </si>
   <si>
     <t>2026-10-27T16:53:50.152964Z</t>
+  </si>
+  <si>
+    <t>2026-10-27T21:30:33.541938Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1574,7 +1577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4781,8 +4784,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="6">
+        <v>1013.354553222656</v>
+      </c>
+      <c r="F135" s="6">
+        <v>3.068128108978271</v>
+      </c>
+      <c r="G135" s="6">
+        <v>2</v>
+      </c>
+      <c r="H135" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="I135" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I134"/>
+  <autoFilter ref="A2:I135"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4804,7 +4830,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4819,39 +4845,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4877,17 +4903,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4895,145 +4921,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5041,56 +5067,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="246">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -561,6 +561,9 @@
   </si>
   <si>
     <t>2026-10-27T21:30:33.541938Z</t>
+  </si>
+  <si>
+    <t>2026-10-28T00:45:12.416447Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1577,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I135"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4807,8 +4810,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B136" s="4"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="6">
+        <v>326.4940490722656</v>
+      </c>
+      <c r="F136" s="6">
+        <v>2.406035423278809</v>
+      </c>
+      <c r="G136" s="6">
+        <v>2</v>
+      </c>
+      <c r="H136" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="I136" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I135"/>
+  <autoFilter ref="A2:I136"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4830,7 +4856,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4845,39 +4871,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4903,17 +4929,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4921,145 +4947,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5067,56 +5093,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="247">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -564,6 +564,9 @@
   </si>
   <si>
     <t>2026-10-28T00:45:12.416447Z</t>
+  </si>
+  <si>
+    <t>2026-10-28T07:24:55.535977Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1580,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4833,8 +4836,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B137" s="4"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="6">
+        <v>409.0936889648438</v>
+      </c>
+      <c r="F137" s="6">
+        <v>0.3562467992305756</v>
+      </c>
+      <c r="G137" s="6">
+        <v>2</v>
+      </c>
+      <c r="H137" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="I137" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I136"/>
+  <autoFilter ref="A2:I137"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4856,7 +4882,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4871,39 +4897,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4929,17 +4955,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4947,145 +4973,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5093,56 +5119,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="248">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -567,6 +567,9 @@
   </si>
   <si>
     <t>2026-10-28T07:24:55.535977Z</t>
+  </si>
+  <si>
+    <t>2026-10-28T14:31:25.635631Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1583,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4859,8 +4862,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B138" s="4"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="6">
+        <v>1556.469116210938</v>
+      </c>
+      <c r="F138" s="6">
+        <v>2.778248071670532</v>
+      </c>
+      <c r="G138" s="6">
+        <v>2</v>
+      </c>
+      <c r="H138" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="I138" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I137"/>
+  <autoFilter ref="A2:I138"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4882,7 +4908,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4897,39 +4923,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4955,17 +4981,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4973,145 +4999,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5119,56 +5145,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -13,15 +13,15 @@
     <sheet name="Method_Legend" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="252">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -101,33 +101,45 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-10-28T15:54:00Z</t>
+  </si>
+  <si>
+    <t>GOES-18</t>
+  </si>
+  <si>
+    <t>instrument/product</t>
+  </si>
+  <si>
+    <t>anomaly/outage</t>
+  </si>
+  <si>
+    <t>INSTRUMENT</t>
+  </si>
+  <si>
+    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: GOES-18 Channel 16 ABI Product Degradation - Issued: October 28, 2026 1554Z</t>
+  </si>
+  <si>
+    <t>Temporal association only; causality NOT established.</t>
+  </si>
+  <si>
+    <t>NOAA OSPO satellite messages</t>
+  </si>
+  <si>
     <t>2026-10-12T13:00:00Z</t>
   </si>
   <si>
-    <t>GOES-18</t>
-  </si>
-  <si>
     <t>product/data</t>
   </si>
   <si>
-    <t>anomaly/outage</t>
-  </si>
-  <si>
     <t>PRODUCT_DATA</t>
   </si>
   <si>
-    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: Correction: GOES-18, 19 - GOES-18, 19 products delivered to PDA Issued: Oct 12, 2026 1300Z</t>
   </si>
   <si>
-    <t>Temporal association only; causality NOT established.</t>
-  </si>
-  <si>
-    <t>NOAA OSPO satellite messages</t>
-  </si>
-  <si>
     <t>2026-10-12T11:47:00Z</t>
   </si>
   <si>
@@ -572,6 +584,9 @@
     <t>2026-10-28T14:31:25.635631Z</t>
   </si>
   <si>
+    <t>2026-10-28T19:52:56.343886Z</t>
+  </si>
+  <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
   </si>
   <si>
@@ -720,9 +735,6 @@
   </si>
   <si>
     <t>Telemetry / command / communications category</t>
-  </si>
-  <si>
-    <t>INSTRUMENT</t>
   </si>
   <si>
     <t>#FFB14E</t>
@@ -856,6 +868,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFB14E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE6A84C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -893,12 +911,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4C8CFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFB14E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -966,7 +978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -986,7 +998,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -994,6 +1008,7 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1292,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1456,46 +1471,32 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="6">
-        <v>0.67</v>
-      </c>
-      <c r="I4" s="6">
-        <v>3.25</v>
-      </c>
-      <c r="J4" s="6">
-        <v>469.21</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="6">
-        <v>1.33</v>
-      </c>
-      <c r="N4" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="O4" s="6">
-        <v>608.65</v>
-      </c>
-      <c r="P4" s="6">
-        <v>3.33</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="R4" s="6">
-        <v>631.91</v>
-      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="6">
+        <v>1556.469116210938</v>
+      </c>
+      <c r="L4" s="6">
+        <v>2.778248071670532</v>
+      </c>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
       <c r="S4" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T4" s="6">
-        <v>-29.83</v>
+        <v>-7.48</v>
       </c>
       <c r="U4" s="6">
-        <v>904.2</v>
+        <v>397.21</v>
       </c>
       <c r="V4" s="6">
-        <v>94.2</v>
+        <v>23.2</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
@@ -1512,36 +1513,36 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>30</v>
+      <c r="E5" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" s="6">
         <v>0.67</v>
       </c>
       <c r="I5" s="6">
-        <v>0.83</v>
+        <v>3.25</v>
       </c>
       <c r="J5" s="6">
-        <v>460.6</v>
+        <v>469.21</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="6">
-        <v>3.33</v>
+        <v>1.33</v>
       </c>
       <c r="N5" s="6">
-        <v>-3.01</v>
+        <v>-1.12</v>
       </c>
       <c r="O5" s="6">
         <v>608.65</v>
@@ -1574,8 +1575,78 @@
         <v>34</v>
       </c>
     </row>
+    <row r="6" spans="1:24">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.83</v>
+      </c>
+      <c r="J6" s="6">
+        <v>460.6</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="N6" s="6">
+        <v>-3.01</v>
+      </c>
+      <c r="O6" s="6">
+        <v>608.65</v>
+      </c>
+      <c r="P6" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="R6" s="6">
+        <v>631.91</v>
+      </c>
+      <c r="S6" s="6">
+        <v>7</v>
+      </c>
+      <c r="T6" s="6">
+        <v>-29.83</v>
+      </c>
+      <c r="U6" s="6">
+        <v>904.2</v>
+      </c>
+      <c r="V6" s="6">
+        <v>94.2</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:X5"/>
+  <autoFilter ref="A3:X6"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -1586,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1595,7 +1666,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1608,36 +1679,36 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B3" s="6">
         <v>0.67</v>
@@ -1666,7 +1737,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1689,7 +1760,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1712,7 +1783,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1735,7 +1806,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1758,7 +1829,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1781,7 +1852,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1804,7 +1875,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B10" s="6">
         <v>0.67</v>
@@ -1833,7 +1904,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1856,7 +1927,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1879,7 +1950,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1902,7 +1973,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="6">
@@ -1929,7 +2000,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1952,7 +2023,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1975,7 +2046,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1998,7 +2069,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B18" s="6">
         <v>5</v>
@@ -2023,7 +2094,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -2046,7 +2117,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -2069,7 +2140,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="6">
@@ -2096,7 +2167,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="6">
@@ -2123,7 +2194,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="6">
@@ -2150,7 +2221,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B24" s="6">
         <v>3.67</v>
@@ -2179,7 +2250,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2202,7 +2273,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2225,7 +2296,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B27" s="6">
         <v>2.67</v>
@@ -2254,7 +2325,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2277,7 +2348,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2300,7 +2371,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2323,7 +2394,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2346,7 +2417,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B32" s="6">
         <v>1</v>
@@ -2375,7 +2446,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2398,7 +2469,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2421,7 +2492,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2444,7 +2515,7 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B36" s="6">
         <v>1.33</v>
@@ -2473,7 +2544,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2496,7 +2567,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2519,7 +2590,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2542,7 +2613,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2565,7 +2636,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2588,7 +2659,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -2611,7 +2682,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="6">
@@ -2638,7 +2709,7 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B44" s="6">
         <v>6.67</v>
@@ -2667,7 +2738,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -2690,7 +2761,7 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -2713,7 +2784,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2736,7 +2807,7 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B48" s="6">
         <v>2.33</v>
@@ -2765,7 +2836,7 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2788,7 +2859,7 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2811,7 +2882,7 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2834,7 +2905,7 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B52" s="6">
         <v>2</v>
@@ -2861,7 +2932,7 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2884,7 +2955,7 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2907,7 +2978,7 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2930,7 +3001,7 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2953,7 +3024,7 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2976,7 +3047,7 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2999,7 +3070,7 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B59" s="6">
         <v>2.33</v>
@@ -3022,7 +3093,7 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="6">
@@ -3049,7 +3120,7 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3070,7 +3141,7 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3093,7 +3164,7 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="6">
@@ -3120,7 +3191,7 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3143,7 +3214,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3166,7 +3237,7 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3189,7 +3260,7 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B67" s="6">
         <v>2.33</v>
@@ -3218,7 +3289,7 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3241,7 +3312,7 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3264,7 +3335,7 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3287,7 +3358,7 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3310,7 +3381,7 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3333,7 +3404,7 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3356,7 +3427,7 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3379,7 +3450,7 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="6">
@@ -3406,7 +3477,7 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3429,7 +3500,7 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -3452,7 +3523,7 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -3475,7 +3546,7 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -3498,7 +3569,7 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -3521,7 +3592,7 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="6">
@@ -3548,7 +3619,7 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -3571,7 +3642,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -3594,7 +3665,7 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -3617,7 +3688,7 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3640,7 +3711,7 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -3663,7 +3734,7 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="6">
@@ -3690,7 +3761,7 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -3713,7 +3784,7 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -3736,7 +3807,7 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -3759,7 +3830,7 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -3782,7 +3853,7 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -3805,7 +3876,7 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B93" s="6">
         <v>0.67</v>
@@ -3834,7 +3905,7 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3857,7 +3928,7 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3880,7 +3951,7 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3903,7 +3974,7 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3926,7 +3997,7 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3949,7 +4020,7 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3972,7 +4043,7 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3995,7 +4066,7 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="4" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4018,7 +4089,7 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4041,7 +4112,7 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B103" s="6">
         <v>3.67</v>
@@ -4070,7 +4141,7 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4093,7 +4164,7 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4116,7 +4187,7 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B106" s="6">
         <v>4.33</v>
@@ -4141,7 +4212,7 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4164,7 +4235,7 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="4" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4187,7 +4258,7 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4210,7 +4281,7 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4233,7 +4304,7 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4256,7 +4327,7 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4279,7 +4350,7 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4302,7 +4373,7 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4325,7 +4396,7 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4348,7 +4419,7 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4371,7 +4442,7 @@
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4394,7 +4465,7 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B118" s="6">
         <v>1.67</v>
@@ -4423,7 +4494,7 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4446,7 +4517,7 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4469,7 +4540,7 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4492,7 +4563,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4515,7 +4586,7 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B123" s="4"/>
       <c r="C123" s="6">
@@ -4542,7 +4613,7 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4565,7 +4636,7 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4588,7 +4659,7 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4611,7 +4682,7 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4634,7 +4705,7 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4657,7 +4728,7 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -4680,7 +4751,7 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -4703,7 +4774,7 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -4726,7 +4797,7 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -4749,7 +4820,7 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -4772,7 +4843,7 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -4795,7 +4866,7 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -4818,7 +4889,7 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -4841,7 +4912,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4864,7 +4935,7 @@
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4885,8 +4956,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="6">
+        <v>1145.908325195312</v>
+      </c>
+      <c r="F139" s="6">
+        <v>10.19226264953613</v>
+      </c>
+      <c r="G139" s="6">
+        <v>2</v>
+      </c>
+      <c r="H139" s="6">
+        <v>-6.91</v>
+      </c>
+      <c r="I139" s="6">
+        <v>404.11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I138"/>
+  <autoFilter ref="A2:I139"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -4908,7 +5002,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4923,39 +5017,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -4981,17 +5075,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -4999,202 +5093,202 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>224</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>227</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>228</v>
+        <v>232</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>231</v>
+        <v>235</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>236</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>234</v>
+        <v>30</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>238</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>236</v>
+        <v>37</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>239</v>
+        <v>242</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>243</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="16" t="s">
-        <v>242</v>
+      <c r="A24" s="17" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="16" t="s">
-        <v>243</v>
+      <c r="A25" s="17" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="16" t="s">
-        <v>244</v>
+      <c r="A26" s="17" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="16" t="s">
-        <v>245</v>
+      <c r="A27" s="17" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="16" t="s">
-        <v>246</v>
+      <c r="A28" s="17" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="16" t="s">
-        <v>247</v>
+      <c r="A29" s="17" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="253">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -585,6 +585,9 @@
   </si>
   <si>
     <t>2026-10-28T19:52:56.343886Z</t>
+  </si>
+  <si>
+    <t>2026-10-29T00:24:33.703536Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1471,32 +1474,50 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="H4" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="I4" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="J4" s="6">
+        <v>391.81</v>
+      </c>
       <c r="K4" s="6">
         <v>1556.469116210938</v>
       </c>
       <c r="L4" s="6">
         <v>2.778248071670532</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="M4" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="N4" s="6">
+        <v>-3.66</v>
+      </c>
+      <c r="O4" s="6">
+        <v>440.31</v>
+      </c>
+      <c r="P4" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>-6.07</v>
+      </c>
+      <c r="R4" s="6">
+        <v>548.98</v>
+      </c>
       <c r="S4" s="6">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="T4" s="6">
         <v>-7.48</v>
       </c>
       <c r="U4" s="6">
-        <v>397.21</v>
+        <v>548.98</v>
       </c>
       <c r="V4" s="6">
-        <v>23.2</v>
+        <v>40.1</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
@@ -1657,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -4979,8 +5000,31 @@
         <v>404.11</v>
       </c>
     </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B140" s="4"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="6">
+        <v>232.623046875</v>
+      </c>
+      <c r="F140" s="6">
+        <v>2.518235921859741</v>
+      </c>
+      <c r="G140" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H140" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I140" s="6">
+        <v>439.08</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I139"/>
+  <autoFilter ref="A2:I140"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5002,7 +5046,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5017,39 +5061,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5075,17 +5119,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5093,134 +5137,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5228,10 +5272,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5239,56 +5283,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="254">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -588,6 +588,9 @@
   </si>
   <si>
     <t>2026-10-29T00:24:33.703536Z</t>
+  </si>
+  <si>
+    <t>2026-10-29T06:28:10.627351Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1678,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5023,8 +5026,31 @@
         <v>439.08</v>
       </c>
     </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="6">
+        <v>180.40087890625</v>
+      </c>
+      <c r="F141" s="6">
+        <v>0.2904369831085205</v>
+      </c>
+      <c r="G141" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H141" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I141" s="6">
+        <v>448.34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I140"/>
+  <autoFilter ref="A2:I141"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5046,7 +5072,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5061,39 +5087,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5119,17 +5145,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5137,134 +5163,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5272,10 +5298,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5283,56 +5309,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="255">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -591,6 +591,9 @@
   </si>
   <si>
     <t>2026-10-29T06:28:10.627351Z</t>
+  </si>
+  <si>
+    <t>2026-10-29T13:42:57.071335Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1681,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I141"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5049,8 +5052,31 @@
         <v>448.34</v>
       </c>
     </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="6">
+        <v>648.7806396484375</v>
+      </c>
+      <c r="F142" s="6">
+        <v>0.6507031917572021</v>
+      </c>
+      <c r="G142" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H142" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I142" s="6">
+        <v>456.57</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I141"/>
+  <autoFilter ref="A2:I142"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5072,7 +5098,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5087,39 +5113,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5145,17 +5171,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5163,134 +5189,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5298,10 +5324,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5309,56 +5335,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="256">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>2026-10-29T13:42:57.071335Z</t>
+  </si>
+  <si>
+    <t>2026-10-29T19:28:03.643367Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1684,7 +1687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5075,8 +5078,31 @@
         <v>456.57</v>
       </c>
     </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="6">
+        <v>684.966796875</v>
+      </c>
+      <c r="F143" s="6">
+        <v>6.637730598449707</v>
+      </c>
+      <c r="G143" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H143" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I143" s="6">
+        <v>463.12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I142"/>
+  <autoFilter ref="A2:I143"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5098,7 +5124,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5113,39 +5139,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5171,17 +5197,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5189,134 +5215,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5324,10 +5350,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5335,56 +5361,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="257">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -597,6 +597,9 @@
   </si>
   <si>
     <t>2026-10-29T19:28:03.643367Z</t>
+  </si>
+  <si>
+    <t>2026-10-29T23:38:46.492802Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1687,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I143"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5101,8 +5104,31 @@
         <v>463.12</v>
       </c>
     </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="6">
+        <v>533.6903686523438</v>
+      </c>
+      <c r="F144" s="6">
+        <v>3.967296123504639</v>
+      </c>
+      <c r="G144" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H144" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I144" s="6">
+        <v>464.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I143"/>
+  <autoFilter ref="A2:I144"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5124,7 +5150,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5139,39 +5165,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5197,17 +5223,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5215,134 +5241,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5350,10 +5376,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5361,56 +5387,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="258">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -600,6 +600,9 @@
   </si>
   <si>
     <t>2026-10-29T23:38:46.492802Z</t>
+  </si>
+  <si>
+    <t>2026-10-30T02:57:39.425662Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1690,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5127,8 +5130,31 @@
         <v>464.75</v>
       </c>
     </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B145" s="4"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="6">
+        <v>416.9647216796875</v>
+      </c>
+      <c r="F145" s="6">
+        <v>0.7685940265655518</v>
+      </c>
+      <c r="G145" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H145" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I145" s="6">
+        <v>464.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I144"/>
+  <autoFilter ref="A2:I145"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5150,7 +5176,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5165,39 +5191,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5223,17 +5249,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5241,134 +5267,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5376,10 +5402,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5387,56 +5413,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="259">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -603,6 +603,9 @@
   </si>
   <si>
     <t>2026-10-30T02:57:39.425662Z</t>
+  </si>
+  <si>
+    <t>2026-10-30T11:01:10.176449Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1693,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5153,8 +5156,31 @@
         <v>464.75</v>
       </c>
     </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="6">
+        <v>370.6621704101562</v>
+      </c>
+      <c r="F146" s="6">
+        <v>1.608158946037292</v>
+      </c>
+      <c r="G146" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H146" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="I146" s="6">
+        <v>464.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I145"/>
+  <autoFilter ref="A2:I146"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5176,7 +5202,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5191,39 +5217,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5249,17 +5275,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5267,134 +5293,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5402,10 +5428,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5413,56 +5439,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="260">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -606,6 +606,9 @@
   </si>
   <si>
     <t>2026-10-30T11:01:10.176449Z</t>
+  </si>
+  <si>
+    <t>2026-10-30T16:50:55.278207Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1696,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I146"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5179,8 +5182,31 @@
         <v>464.75</v>
       </c>
     </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="6">
+        <v>1120.894775390625</v>
+      </c>
+      <c r="F147" s="6">
+        <v>7.232413291931152</v>
+      </c>
+      <c r="G147" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H147" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="I147" s="6">
+        <v>427.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I146"/>
+  <autoFilter ref="A2:I147"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5202,7 +5228,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5217,39 +5243,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5275,17 +5301,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5293,134 +5319,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5428,10 +5454,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5439,56 +5465,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$148</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="261">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -609,6 +609,9 @@
   </si>
   <si>
     <t>2026-10-30T16:50:55.278207Z</t>
+  </si>
+  <si>
+    <t>2026-10-30T21:42:47.114021Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1699,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5205,8 +5208,31 @@
         <v>427.6</v>
       </c>
     </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="6">
+        <v>241.9476165771484</v>
+      </c>
+      <c r="F148" s="6">
+        <v>34.01787567138672</v>
+      </c>
+      <c r="G148" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H148" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="I148" s="6">
+        <v>427.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I147"/>
+  <autoFilter ref="A2:I148"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5228,7 +5254,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5243,39 +5269,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5301,17 +5327,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5319,134 +5345,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5454,10 +5480,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5465,56 +5491,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="262">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -612,6 +612,9 @@
   </si>
   <si>
     <t>2026-10-30T21:42:47.114021Z</t>
+  </si>
+  <si>
+    <t>2026-10-31T01:07:17.397373Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1702,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5231,8 +5234,31 @@
         <v>427.6</v>
       </c>
     </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="6">
+        <v>137.6469116210938</v>
+      </c>
+      <c r="F149" s="6">
+        <v>13.81884288787842</v>
+      </c>
+      <c r="G149" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H149" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="I149" s="6">
+        <v>427.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I148"/>
+  <autoFilter ref="A2:I149"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5254,7 +5280,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5269,39 +5295,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5327,17 +5353,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5345,134 +5371,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5480,10 +5506,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5491,56 +5517,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="263">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -615,6 +615,9 @@
   </si>
   <si>
     <t>2026-10-31T01:07:17.397373Z</t>
+  </si>
+  <si>
+    <t>2026-10-31T07:30:53.220027Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1705,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5257,8 +5260,31 @@
         <v>427.6</v>
       </c>
     </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B150" s="4"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="6">
+        <v>31.36667633056641</v>
+      </c>
+      <c r="F150" s="6">
+        <v>0.9698914885520935</v>
+      </c>
+      <c r="G150" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H150" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="I150" s="6">
+        <v>427.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I149"/>
+  <autoFilter ref="A2:I150"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5280,7 +5306,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5295,39 +5321,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5353,17 +5379,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5371,134 +5397,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5506,10 +5532,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5517,56 +5543,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-10_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="264">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-10</t>
   </si>
@@ -618,6 +618,9 @@
   </si>
   <si>
     <t>2026-10-31T07:30:53.220027Z</t>
+  </si>
+  <si>
+    <t>2026-10-31T13:53:42.571786Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1708,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -5283,8 +5286,31 @@
         <v>427.6</v>
       </c>
     </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B151" s="4"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="6">
+        <v>276.5582275390625</v>
+      </c>
+      <c r="F151" s="6">
+        <v>0.7304256558418274</v>
+      </c>
+      <c r="G151" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H151" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="I151" s="6">
+        <v>427.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I150"/>
+  <autoFilter ref="A2:I151"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -5306,7 +5332,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5321,39 +5347,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -5379,17 +5405,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -5397,134 +5423,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5532,10 +5558,10 @@
         <v>30</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -5543,56 +5569,56 @@
         <v>37</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
